--- a/6_Quality_Appraisal/QualityAppraisal.xlsx
+++ b/6_Quality_Appraisal/QualityAppraisal.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniotrovato/Documents/GitHub/RegressionTestingOptimizationSLR/6_Quality_Appraisal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537CEF5D-01DE-9F45-9B99-AFC8C3E61BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="396" documentId="13_ncr:1_{537CEF5D-01DE-9F45-9B99-AFC8C3E61BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6491A716-9D25-4BEA-BC44-19830BE293CC}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -116,24 +119,36 @@
     <t>Mendoza, Jediael and Mycroft, Jason and Milbury, Lyam and Kahani, Nafiseh and Jaskolka, Jason</t>
   </si>
   <si>
+    <t>Antonio</t>
+  </si>
+  <si>
     <t>A Configurable Test Case Prioritization Technique for Early Fault Detection and Low Test Case Spreading</t>
   </si>
   <si>
     <t>Torres, Wesley and Alves, Everton and Machado, Patricia</t>
   </si>
   <si>
+    <t>Luigi</t>
+  </si>
+  <si>
     <t>Test case prioritization based on neural networks classification</t>
   </si>
   <si>
     <t>Tiutin, Cristina-Maria and Vescan, Andreea</t>
   </si>
   <si>
+    <t>Dario</t>
+  </si>
+  <si>
     <t>Black-box Test Case Selection by Relating Code Changes with Previously Fixed Defects</t>
   </si>
   <si>
     <t>\c{C}\i{}ng\i{}l, Tutku and S\"{o}zer, Hasan</t>
   </si>
   <si>
+    <t>Carmine</t>
+  </si>
+  <si>
     <t>A Systematic Literature Review on Test Case Prioritization in Combinatorial Testing</t>
   </si>
   <si>
@@ -1776,25 +1791,13 @@
   </si>
   <si>
     <t>Test Case Prioritization Based on Analysis of Program Structure</t>
-  </si>
-  <si>
-    <t>Antonio</t>
-  </si>
-  <si>
-    <t>Luigi</t>
-  </si>
-  <si>
-    <t>Dario</t>
-  </si>
-  <si>
-    <t>Carmine</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1803,7 +1806,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1834,6 +1837,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1847,12 +1862,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2156,9 +2173,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V365"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63.7109375" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2217,7 +2238,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2262,7 +2283,7 @@
         <v>0.76666666666666661</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -2289,7 +2310,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -2334,7 +2355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -2373,16 +2394,16 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U5" t="s">
-        <v>581</v>
+        <v>27</v>
       </c>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>0.4</v>
@@ -2416,26 +2437,32 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U6" t="s">
-        <v>582</v>
+        <v>30</v>
       </c>
       <c r="V6" s="2"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>0.4</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4">
+        <v>0.6</v>
+      </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="4"/>
+      <c r="G7" s="4">
+        <v>1</v>
+      </c>
       <c r="H7" s="1"/>
-      <c r="I7" s="4"/>
+      <c r="I7" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="4"/>
       <c r="L7" s="1"/>
@@ -2446,9 +2473,9 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q7" t="e">
+      <c r="Q7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.73333333333333339</v>
       </c>
       <c r="R7" t="e">
         <f t="shared" si="2"/>
@@ -2459,16 +2486,16 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U7" t="s">
-        <v>583</v>
+        <v>33</v>
       </c>
       <c r="V7" s="3"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2502,39 +2529,51 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U8" t="s">
-        <v>584</v>
+        <v>36</v>
       </c>
       <c r="V8" s="4"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C9">
         <v>0.4</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="4"/>
+      <c r="G9" s="4">
+        <v>1</v>
+      </c>
       <c r="H9" s="2"/>
-      <c r="I9" s="4"/>
+      <c r="I9" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="4"/>
+      <c r="K9" s="4">
+        <v>0.6</v>
+      </c>
       <c r="L9" s="2"/>
-      <c r="M9" s="4"/>
+      <c r="M9" s="4">
+        <v>0.3</v>
+      </c>
       <c r="N9" s="2"/>
-      <c r="O9" s="4"/>
+      <c r="O9" s="4">
+        <v>0.6</v>
+      </c>
       <c r="P9" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q9" t="e">
+      <c r="Q9">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.68333333333333324</v>
       </c>
       <c r="R9" t="e">
         <f t="shared" si="2"/>
@@ -2545,22 +2584,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>0.5</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="4"/>
+      <c r="I10" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J10" s="3"/>
       <c r="K10" s="4"/>
       <c r="L10" s="3"/>
@@ -2571,9 +2616,9 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q10" t="e">
+      <c r="Q10">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="R10" t="e">
         <f t="shared" si="2"/>
@@ -2584,12 +2629,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C11">
         <v>0.4</v>
@@ -2623,12 +2668,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C12">
         <v>0.4</v>
@@ -2662,22 +2707,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C13">
         <v>0.4</v>
       </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="4"/>
+      <c r="E13" s="4">
+        <v>0.3</v>
+      </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="4"/>
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="4"/>
+      <c r="I13" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="4"/>
       <c r="L13" s="1"/>
@@ -2688,9 +2739,9 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q13" t="e">
+      <c r="Q13">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="R13" t="e">
         <f t="shared" si="2"/>
@@ -2701,12 +2752,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C14">
         <v>0.4</v>
@@ -2740,22 +2791,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="4"/>
+      <c r="G15" s="4">
+        <v>1</v>
+      </c>
       <c r="H15" s="2"/>
-      <c r="I15" s="4"/>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="4"/>
       <c r="L15" s="2"/>
@@ -2766,9 +2823,9 @@
         <f>AVERAGE(D15,F15,H15,J15,L15,N15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q15" t="e">
+      <c r="Q15">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R15" t="e">
         <f t="shared" si="2"/>
@@ -2779,22 +2836,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C16">
         <v>0.4</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
+      <c r="G16" s="4">
+        <v>1</v>
+      </c>
       <c r="H16" s="3"/>
-      <c r="I16" s="4"/>
+      <c r="I16" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J16" s="3"/>
       <c r="K16" s="4"/>
       <c r="L16" s="3"/>
@@ -2805,9 +2868,9 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q16" t="e">
+      <c r="Q16">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R16" t="e">
         <f t="shared" si="2"/>
@@ -2818,12 +2881,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2857,12 +2920,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2896,12 +2959,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C19">
         <v>0.5</v>
@@ -2941,22 +3004,28 @@
         <v>0.58333333333333326</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C20">
         <v>0.4</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="4"/>
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="4"/>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="4"/>
+      <c r="I20" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J20" s="1"/>
       <c r="K20" s="4"/>
       <c r="L20" s="1"/>
@@ -2967,9 +3036,9 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q20" t="e">
+      <c r="Q20">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="R20" t="e">
         <f t="shared" si="2"/>
@@ -2980,12 +3049,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C21">
         <v>0.4</v>
@@ -3025,12 +3094,12 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -3070,12 +3139,12 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C23">
         <v>0.4</v>
@@ -3109,22 +3178,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C24">
         <v>0.4</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="E24" s="4"/>
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
       <c r="F24" s="2"/>
-      <c r="G24" s="4"/>
+      <c r="G24" s="4">
+        <v>1</v>
+      </c>
       <c r="H24" s="2"/>
-      <c r="I24" s="4"/>
+      <c r="I24" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J24" s="2"/>
       <c r="K24" s="4"/>
       <c r="L24" s="2"/>
@@ -3135,9 +3210,9 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q24" t="e">
+      <c r="Q24">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="R24" t="e">
         <f t="shared" si="2"/>
@@ -3148,22 +3223,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
       <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="4"/>
+      <c r="I25" s="4">
+        <v>1</v>
+      </c>
       <c r="J25" s="3"/>
       <c r="K25" s="4"/>
       <c r="L25" s="3"/>
@@ -3174,9 +3255,9 @@
         <f>AVERAGE(D25,F25,H25,J25,L25,N25)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q25" t="e">
+      <c r="Q25">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R25" t="e">
         <f t="shared" si="2"/>
@@ -3187,12 +3268,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -3232,12 +3313,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C27">
         <v>0.4</v>
@@ -3271,12 +3352,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C28">
         <v>0.4</v>
@@ -3316,12 +3397,12 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C29">
         <v>0.4</v>
@@ -3355,12 +3436,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -3400,12 +3481,12 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C31">
         <v>0.8</v>
@@ -3445,22 +3526,28 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" s="1"/>
-      <c r="E32" s="4"/>
+      <c r="E32" s="4">
+        <v>1</v>
+      </c>
       <c r="F32" s="1"/>
-      <c r="G32" s="4"/>
+      <c r="G32" s="4">
+        <v>1</v>
+      </c>
       <c r="H32" s="1"/>
-      <c r="I32" s="4"/>
+      <c r="I32" s="4">
+        <v>1</v>
+      </c>
       <c r="J32" s="1"/>
       <c r="K32" s="4"/>
       <c r="L32" s="1"/>
@@ -3471,9 +3558,9 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q32" t="e">
+      <c r="Q32">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R32" t="e">
         <f t="shared" si="2"/>
@@ -3484,12 +3571,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19">
       <c r="A33" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -3523,12 +3610,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -3568,35 +3655,47 @@
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" s="2"/>
-      <c r="E35" s="4"/>
+      <c r="E35" s="4">
+        <v>1</v>
+      </c>
       <c r="F35" s="2"/>
-      <c r="G35" s="4"/>
+      <c r="G35" s="4">
+        <v>0.6</v>
+      </c>
       <c r="H35" s="2"/>
-      <c r="I35" s="4"/>
+      <c r="I35" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J35" s="2"/>
-      <c r="K35" s="4"/>
+      <c r="K35" s="4">
+        <v>1</v>
+      </c>
       <c r="L35" s="2"/>
-      <c r="M35" s="4"/>
+      <c r="M35" s="4">
+        <v>0.6</v>
+      </c>
       <c r="N35" s="2"/>
-      <c r="O35" s="4"/>
+      <c r="O35" s="4">
+        <v>0</v>
+      </c>
       <c r="P35" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q35" t="e">
+      <c r="Q35">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.63333333333333341</v>
       </c>
       <c r="R35" t="e">
         <f t="shared" si="2"/>
@@ -3607,22 +3706,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" s="3"/>
-      <c r="E36" s="4"/>
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
       <c r="F36" s="3"/>
-      <c r="G36" s="4"/>
+      <c r="G36" s="4">
+        <v>1</v>
+      </c>
       <c r="H36" s="3"/>
-      <c r="I36" s="4"/>
+      <c r="I36" s="4">
+        <v>1</v>
+      </c>
       <c r="J36" s="3"/>
       <c r="K36" s="4"/>
       <c r="L36" s="3"/>
@@ -3633,9 +3738,9 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q36" t="e">
+      <c r="Q36">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R36" t="e">
         <f t="shared" si="2"/>
@@ -3646,12 +3751,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C37">
         <v>0.4</v>
@@ -3685,12 +3790,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19">
       <c r="A38" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C38">
         <v>0.4</v>
@@ -3730,12 +3835,12 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C39">
         <v>0.4</v>
@@ -3787,12 +3892,12 @@
         <v>0.29000000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C40">
         <v>0.5</v>
@@ -3832,12 +3937,12 @@
         <v>0.54166666666666674</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19">
       <c r="A41" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C41">
         <v>0.4</v>
@@ -3871,12 +3976,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C42">
         <v>0.4</v>
@@ -3916,12 +4021,12 @@
         <v>0.51666666666666672</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C43">
         <v>0.4</v>
@@ -3961,22 +4066,28 @@
         <v>0.58333333333333326</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44" s="1"/>
-      <c r="E44" s="4"/>
+      <c r="E44" s="4">
+        <v>0.3</v>
+      </c>
       <c r="F44" s="1"/>
-      <c r="G44" s="4"/>
+      <c r="G44" s="4">
+        <v>0</v>
+      </c>
       <c r="H44" s="1"/>
-      <c r="I44" s="4"/>
+      <c r="I44" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J44" s="1"/>
       <c r="K44" s="4"/>
       <c r="L44" s="1"/>
@@ -3987,9 +4098,9 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q44" t="e">
+      <c r="Q44">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.3</v>
       </c>
       <c r="R44" t="e">
         <f t="shared" si="2"/>
@@ -4000,12 +4111,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19">
       <c r="A45" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C45">
         <v>0.5</v>
@@ -4057,12 +4168,12 @@
         <v>0.60499999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19">
       <c r="A46" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B46" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C46">
         <v>0.8</v>
@@ -4102,12 +4213,12 @@
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C47">
         <v>0.4</v>
@@ -4141,12 +4252,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C48">
         <v>0.4</v>
@@ -4198,12 +4309,12 @@
         <v>0.36499999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:19">
       <c r="A49" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C49">
         <v>0.4</v>
@@ -4243,22 +4354,28 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C50">
         <v>0.4</v>
       </c>
       <c r="D50" s="2"/>
-      <c r="E50" s="4"/>
+      <c r="E50" s="4">
+        <v>0</v>
+      </c>
       <c r="F50" s="2"/>
-      <c r="G50" s="4"/>
+      <c r="G50" s="4">
+        <v>0</v>
+      </c>
       <c r="H50" s="2"/>
-      <c r="I50" s="4"/>
+      <c r="I50" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J50" s="2"/>
       <c r="K50" s="4"/>
       <c r="L50" s="2"/>
@@ -4269,9 +4386,9 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q50" t="e">
+      <c r="Q50">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="R50" t="e">
         <f t="shared" si="2"/>
@@ -4282,12 +4399,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19">
       <c r="A51" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B51" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C51">
         <v>0.4</v>
@@ -4327,12 +4444,12 @@
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B52" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C52">
         <v>0.5</v>
@@ -4390,12 +4507,12 @@
         <v>0.71666666666666656</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:19">
       <c r="A53" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C53">
         <v>0.4</v>
@@ -4435,22 +4552,28 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:19">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C54">
         <v>0.8</v>
       </c>
       <c r="D54" s="3"/>
-      <c r="E54" s="4"/>
+      <c r="E54" s="4">
+        <v>0</v>
+      </c>
       <c r="F54" s="3"/>
-      <c r="G54" s="4"/>
+      <c r="G54" s="4">
+        <v>0</v>
+      </c>
       <c r="H54" s="3"/>
-      <c r="I54" s="4"/>
+      <c r="I54" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J54" s="3"/>
       <c r="K54" s="4"/>
       <c r="L54" s="3"/>
@@ -4461,9 +4584,9 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q54" t="e">
+      <c r="Q54">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="R54" t="e">
         <f t="shared" si="2"/>
@@ -4474,12 +4597,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:19">
       <c r="A55" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C55">
         <v>0.4</v>
@@ -4519,12 +4642,12 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:19">
       <c r="A56" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C56">
         <v>0.8</v>
@@ -4564,12 +4687,12 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:19">
       <c r="A57" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B57" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C57">
         <v>0.4</v>
@@ -4609,12 +4732,12 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B58" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C58">
         <v>0.4</v>
@@ -4669,12 +4792,12 @@
         <v>0.41416666666666668</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B59" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C59">
         <v>0.4</v>
@@ -4714,12 +4837,12 @@
         <v>0.58333333333333326</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B60" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C60">
         <v>0.5</v>
@@ -4759,12 +4882,12 @@
         <v>0.60833333333333328</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:19">
       <c r="A61" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C61">
         <v>0.5</v>
@@ -4804,12 +4927,12 @@
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -4849,12 +4972,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19">
       <c r="A63" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C63">
         <v>0.4</v>
@@ -4894,12 +5017,12 @@
         <v>0.51666666666666661</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19">
       <c r="A64" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B64" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C64">
         <v>0.4</v>
@@ -4939,12 +5062,12 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:19">
       <c r="A65" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B65" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C65">
         <v>0.4</v>
@@ -4996,12 +5119,12 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:19">
       <c r="A66" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B66" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C66">
         <v>0.4</v>
@@ -5047,12 +5170,12 @@
         <v>0.48749999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:19">
       <c r="A67" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B67" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -5092,12 +5215,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:19">
       <c r="A68" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B68" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C68">
         <v>0.4</v>
@@ -5137,12 +5260,12 @@
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:19">
       <c r="A69" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -5182,12 +5305,12 @@
         <v>0.76666666666666661</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:19">
       <c r="A70" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B70" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -5227,12 +5350,12 @@
         <v>0.7416666666666667</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:19">
       <c r="A71" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C71">
         <v>0.4</v>
@@ -5266,12 +5389,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:19">
       <c r="A72" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -5305,12 +5428,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:19">
       <c r="A73" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B73" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C73">
         <v>0.4</v>
@@ -5350,22 +5473,28 @@
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B74" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C74">
         <v>0.4</v>
       </c>
       <c r="D74" s="1"/>
-      <c r="E74" s="4"/>
+      <c r="E74" s="4">
+        <v>0</v>
+      </c>
       <c r="F74" s="1"/>
-      <c r="G74" s="4"/>
+      <c r="G74" s="4">
+        <v>1</v>
+      </c>
       <c r="H74" s="1"/>
-      <c r="I74" s="4"/>
+      <c r="I74" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J74" s="1"/>
       <c r="K74" s="4"/>
       <c r="L74" s="1"/>
@@ -5376,9 +5505,9 @@
         <f>AVERAGE(D74,F74,H74,J74,L74,N74)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q74" t="e">
+      <c r="Q74">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R74" t="e">
         <f t="shared" si="5"/>
@@ -5389,12 +5518,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:19">
       <c r="A75" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C75">
         <v>0.4</v>
@@ -5434,12 +5563,12 @@
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19">
       <c r="A76" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B76" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C76">
         <v>0.4</v>
@@ -5479,12 +5608,12 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B77" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C77">
         <v>0.4</v>
@@ -5524,12 +5653,12 @@
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:19">
       <c r="A78" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B78" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C78">
         <v>0.4</v>
@@ -5569,12 +5698,12 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:19">
       <c r="A79" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B79" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C79">
         <v>0.4</v>
@@ -5608,12 +5737,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:19">
       <c r="A80" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B80" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C80">
         <v>0.5</v>
@@ -5653,12 +5782,12 @@
         <v>0.56666666666666665</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19">
       <c r="A81" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C81">
         <v>0.4</v>
@@ -5698,35 +5827,47 @@
         <v>0.51666666666666672</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19">
       <c r="A82" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B82" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82" s="2"/>
-      <c r="E82" s="4"/>
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
       <c r="F82" s="2"/>
-      <c r="G82" s="4"/>
+      <c r="G82" s="4">
+        <v>1</v>
+      </c>
       <c r="H82" s="2"/>
-      <c r="I82" s="4"/>
+      <c r="I82" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J82" s="2"/>
-      <c r="K82" s="4"/>
+      <c r="K82" s="4">
+        <v>0.6</v>
+      </c>
       <c r="L82" s="2"/>
-      <c r="M82" s="4"/>
+      <c r="M82" s="4">
+        <v>0.6</v>
+      </c>
       <c r="N82" s="2"/>
-      <c r="O82" s="4"/>
+      <c r="O82" s="4">
+        <v>0.3</v>
+      </c>
       <c r="P82" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q82" t="e">
+      <c r="Q82">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0.68333333333333346</v>
       </c>
       <c r="R82" t="e">
         <f t="shared" si="5"/>
@@ -5737,12 +5878,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19">
       <c r="A83" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B83" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C83">
         <v>0.5</v>
@@ -5782,12 +5923,12 @@
         <v>0.41666666666666663</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:19">
       <c r="A84" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B84" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C84">
         <v>0.8</v>
@@ -5827,12 +5968,12 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19">
       <c r="A85" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B85" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C85">
         <v>0.4</v>
@@ -5872,12 +6013,12 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:19">
       <c r="A86" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B86" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C86">
         <v>0.4</v>
@@ -5917,12 +6058,12 @@
         <v>0.58333333333333326</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:19">
       <c r="A87" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B87" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -5962,12 +6103,12 @@
         <v>0.81666666666666665</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19">
       <c r="A88" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B88" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C88">
         <v>0.4</v>
@@ -6007,12 +6148,12 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B89" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C89">
         <v>0.4</v>
@@ -6052,12 +6193,12 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:19">
       <c r="A90" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B90" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C90">
         <v>0.4</v>
@@ -6097,22 +6238,28 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:19">
       <c r="A91" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B91" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
       <c r="D91" s="3"/>
-      <c r="E91" s="4"/>
+      <c r="E91" s="4">
+        <v>1</v>
+      </c>
       <c r="F91" s="3"/>
-      <c r="G91" s="4"/>
+      <c r="G91" s="4">
+        <v>1</v>
+      </c>
       <c r="H91" s="3"/>
-      <c r="I91" s="4"/>
+      <c r="I91" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J91" s="3"/>
       <c r="K91" s="4"/>
       <c r="L91" s="3"/>
@@ -6123,9 +6270,9 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q91" t="e">
+      <c r="Q91">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R91" t="e">
         <f t="shared" si="5"/>
@@ -6136,12 +6283,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:19">
       <c r="A92" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B92" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C92">
         <v>0.4</v>
@@ -6175,12 +6322,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:19">
       <c r="A93" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B93" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C93">
         <v>0.4</v>
@@ -6220,12 +6367,12 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:19">
       <c r="A94" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B94" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C94">
         <v>0.5</v>
@@ -6265,12 +6412,12 @@
         <v>0.68333333333333335</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:19">
       <c r="A95" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B95" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -6304,35 +6451,47 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:19">
       <c r="A96" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B96" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C96">
         <v>1</v>
       </c>
       <c r="D96" s="1"/>
-      <c r="E96" s="4"/>
+      <c r="E96" s="4">
+        <v>1</v>
+      </c>
       <c r="F96" s="1"/>
-      <c r="G96" s="4"/>
+      <c r="G96" s="4">
+        <v>1</v>
+      </c>
       <c r="H96" s="1"/>
-      <c r="I96" s="4"/>
+      <c r="I96" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J96" s="1"/>
-      <c r="K96" s="4"/>
+      <c r="K96" s="4">
+        <v>0.6</v>
+      </c>
       <c r="L96" s="1"/>
-      <c r="M96" s="4"/>
+      <c r="M96" s="4">
+        <v>0.6</v>
+      </c>
       <c r="N96" s="1"/>
-      <c r="O96" s="4"/>
+      <c r="O96" s="4">
+        <v>0.3</v>
+      </c>
       <c r="P96" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q96" t="e">
+      <c r="Q96">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.68333333333333346</v>
       </c>
       <c r="R96" t="e">
         <f t="shared" si="5"/>
@@ -6343,12 +6502,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:19">
       <c r="A97" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B97" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -6382,12 +6541,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:19">
       <c r="A98" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B98" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C98">
         <v>0.4</v>
@@ -6427,22 +6586,28 @@
         <v>0.39166666666666666</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19">
       <c r="A99" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B99" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C99">
         <v>1</v>
       </c>
       <c r="D99" s="2"/>
-      <c r="E99" s="4"/>
+      <c r="E99" s="4">
+        <v>1</v>
+      </c>
       <c r="F99" s="2"/>
-      <c r="G99" s="4"/>
+      <c r="G99" s="4">
+        <v>1</v>
+      </c>
       <c r="H99" s="2"/>
-      <c r="I99" s="4"/>
+      <c r="I99" s="4">
+        <v>1</v>
+      </c>
       <c r="J99" s="2"/>
       <c r="K99" s="4"/>
       <c r="L99" s="2"/>
@@ -6453,9 +6618,9 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q99" t="e">
+      <c r="Q99">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R99" t="e">
         <f t="shared" si="5"/>
@@ -6466,12 +6631,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:19">
       <c r="A100" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B100" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C100">
         <v>0.4</v>
@@ -6511,12 +6676,12 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:19">
       <c r="A101" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B101" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C101">
         <v>0.8</v>
@@ -6556,12 +6721,12 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:19">
       <c r="A102" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B102" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C102">
         <v>0.4</v>
@@ -6601,12 +6766,12 @@
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:19">
       <c r="A103" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B103" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C103">
         <v>0.4</v>
@@ -6646,22 +6811,28 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:19">
       <c r="A104" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B104" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="D104" s="3"/>
-      <c r="E104" s="4"/>
+      <c r="E104" s="4">
+        <v>1</v>
+      </c>
       <c r="F104" s="3"/>
-      <c r="G104" s="4"/>
+      <c r="G104" s="4">
+        <v>1</v>
+      </c>
       <c r="H104" s="3"/>
-      <c r="I104" s="4"/>
+      <c r="I104" s="4">
+        <v>1</v>
+      </c>
       <c r="J104" s="3"/>
       <c r="K104" s="4"/>
       <c r="L104" s="3"/>
@@ -6672,9 +6843,9 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q104" t="e">
+      <c r="Q104">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R104" t="e">
         <f t="shared" si="5"/>
@@ -6685,12 +6856,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:19">
       <c r="A105" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B105" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C105">
         <v>0.4</v>
@@ -6730,12 +6901,12 @@
         <v>0.58333333333333326</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19">
       <c r="A106" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B106" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C106">
         <v>0.4</v>
@@ -6775,12 +6946,12 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19">
       <c r="A107" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B107" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C107">
         <v>0.8</v>
@@ -6820,12 +6991,12 @@
         <v>0.73333333333333339</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:19">
       <c r="A108" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B108" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C108">
         <v>0.5</v>
@@ -6865,12 +7036,12 @@
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:19">
       <c r="A109" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B109" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C109">
         <v>0.4</v>
@@ -6910,12 +7081,12 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:19">
       <c r="A110" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B110" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -6955,12 +7126,12 @@
         <v>0.76666666666666661</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:19">
       <c r="A111" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B111" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C111">
         <v>0.4</v>
@@ -7000,12 +7171,12 @@
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:19">
       <c r="A112" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B112" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C112">
         <v>0.5</v>
@@ -7045,12 +7216,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:19">
       <c r="A113" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B113" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C113">
         <v>0.5</v>
@@ -7090,12 +7261,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:19">
       <c r="A114" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B114" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -7135,12 +7306,12 @@
         <v>0.8833333333333333</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:19">
       <c r="A115" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B115" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C115">
         <v>0.5</v>
@@ -7180,12 +7351,12 @@
         <v>0.58333333333333326</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:19">
       <c r="A116" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B116" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C116">
         <v>0.4</v>
@@ -7219,12 +7390,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:19">
       <c r="A117" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B117" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C117">
         <v>0.5</v>
@@ -7264,12 +7435,12 @@
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:19">
       <c r="A118" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B118" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -7303,12 +7474,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:19">
       <c r="A119" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B119" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C119">
         <v>1</v>
@@ -7348,12 +7519,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:19">
       <c r="A120" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B120" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C120">
         <v>0.4</v>
@@ -7393,12 +7564,12 @@
         <v>0.3666666666666667</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:19">
       <c r="A121" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B121" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C121">
         <v>0.4</v>
@@ -7438,12 +7609,12 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:19">
       <c r="A122" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B122" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C122">
         <v>0.5</v>
@@ -7483,22 +7654,28 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:19">
       <c r="A123" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B123" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C123">
         <v>0.4</v>
       </c>
       <c r="D123" s="1"/>
-      <c r="E123" s="4"/>
+      <c r="E123" s="4">
+        <v>1</v>
+      </c>
       <c r="F123" s="1"/>
-      <c r="G123" s="4"/>
+      <c r="G123" s="4">
+        <v>1</v>
+      </c>
       <c r="H123" s="1"/>
-      <c r="I123" s="4"/>
+      <c r="I123" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J123" s="1"/>
       <c r="K123" s="4"/>
       <c r="L123" s="1"/>
@@ -7509,9 +7686,9 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q123" t="e">
+      <c r="Q123">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R123" t="e">
         <f t="shared" si="5"/>
@@ -7522,12 +7699,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:19">
       <c r="A124" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C124">
         <v>0.4</v>
@@ -7567,12 +7744,12 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:19">
       <c r="A125" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B125" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C125">
         <v>1</v>
@@ -7612,12 +7789,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:19">
       <c r="A126" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B126" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -7651,22 +7828,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:19">
       <c r="A127" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B127" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C127">
         <v>1</v>
       </c>
       <c r="D127" s="2"/>
-      <c r="E127" s="4"/>
+      <c r="E127" s="4">
+        <v>0</v>
+      </c>
       <c r="F127" s="2"/>
-      <c r="G127" s="4"/>
+      <c r="G127" s="4">
+        <v>0</v>
+      </c>
       <c r="H127" s="2"/>
-      <c r="I127" s="4"/>
+      <c r="I127" s="4">
+        <v>1</v>
+      </c>
       <c r="J127" s="2"/>
       <c r="K127" s="4"/>
       <c r="L127" s="2"/>
@@ -7677,9 +7860,9 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q127" t="e">
+      <c r="Q127">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="R127" t="e">
         <f t="shared" si="5"/>
@@ -7690,12 +7873,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:19">
       <c r="A128" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B128" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C128">
         <v>0.8</v>
@@ -7735,12 +7918,12 @@
         <v>0.6166666666666667</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:19">
       <c r="A129" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B129" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C129">
         <v>0.5</v>
@@ -7780,22 +7963,28 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:19">
       <c r="A130" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B130" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C130">
         <v>1</v>
       </c>
       <c r="D130" s="3"/>
-      <c r="E130" s="4"/>
+      <c r="E130" s="4">
+        <v>1</v>
+      </c>
       <c r="F130" s="3"/>
-      <c r="G130" s="4"/>
+      <c r="G130" s="4">
+        <v>1</v>
+      </c>
       <c r="H130" s="3"/>
-      <c r="I130" s="4"/>
+      <c r="I130" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J130" s="3"/>
       <c r="K130" s="4"/>
       <c r="L130" s="3"/>
@@ -7806,9 +7995,9 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q130" t="e">
+      <c r="Q130">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R130" t="e">
         <f t="shared" si="5"/>
@@ -7819,12 +8008,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:19">
       <c r="A131" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B131" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -7864,12 +8053,12 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:19">
       <c r="A132" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B132" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -7903,12 +8092,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:19">
       <c r="A133" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B133" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C133">
         <v>0.5</v>
@@ -7948,12 +8137,12 @@
         <v>0.58333333333333326</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:19">
       <c r="A134" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B134" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -7987,12 +8176,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:19">
       <c r="A135" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B135" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C135">
         <v>0.4</v>
@@ -8032,12 +8221,12 @@
         <v>0.58333333333333326</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:19">
       <c r="A136" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B136" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -8077,12 +8266,12 @@
         <v>0.76666666666666661</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:19">
       <c r="A137" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B137" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C137">
         <v>0.4</v>
@@ -8122,22 +8311,28 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:19">
       <c r="A138" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B138" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C138">
         <v>1</v>
       </c>
       <c r="D138" s="1"/>
-      <c r="E138" s="4"/>
+      <c r="E138" s="4">
+        <v>1</v>
+      </c>
       <c r="F138" s="1"/>
-      <c r="G138" s="4"/>
+      <c r="G138" s="4">
+        <v>0</v>
+      </c>
       <c r="H138" s="1"/>
-      <c r="I138" s="4"/>
+      <c r="I138" s="4">
+        <v>1</v>
+      </c>
       <c r="J138" s="1"/>
       <c r="K138" s="4"/>
       <c r="L138" s="1"/>
@@ -8148,9 +8343,9 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q138" t="e">
+      <c r="Q138">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R138" t="e">
         <f t="shared" si="8"/>
@@ -8161,12 +8356,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:19">
       <c r="A139" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B139" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -8206,12 +8401,12 @@
         <v>0.83333333333333326</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:19">
       <c r="A140" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B140" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C140">
         <v>0.4</v>
@@ -8251,12 +8446,12 @@
         <v>0.51666666666666661</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:19">
       <c r="A141" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B141" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -8290,22 +8485,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:19">
       <c r="A142" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B142" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C142">
         <v>0.4</v>
       </c>
       <c r="D142" s="2"/>
-      <c r="E142" s="4"/>
+      <c r="E142" s="4">
+        <v>0</v>
+      </c>
       <c r="F142" s="2"/>
-      <c r="G142" s="4"/>
+      <c r="G142" s="4">
+        <v>1</v>
+      </c>
       <c r="H142" s="2"/>
-      <c r="I142" s="4"/>
+      <c r="I142" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J142" s="2"/>
       <c r="K142" s="4"/>
       <c r="L142" s="2"/>
@@ -8316,9 +8517,9 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q142" t="e">
+      <c r="Q142">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="R142" t="e">
         <f t="shared" si="8"/>
@@ -8329,22 +8530,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:19">
       <c r="A143" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B143" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="D143" s="3"/>
-      <c r="E143" s="4"/>
+      <c r="E143" s="4">
+        <v>0</v>
+      </c>
       <c r="F143" s="3"/>
-      <c r="G143" s="4"/>
+      <c r="G143" s="4">
+        <v>0</v>
+      </c>
       <c r="H143" s="3"/>
-      <c r="I143" s="4"/>
+      <c r="I143" s="4">
+        <v>1</v>
+      </c>
       <c r="J143" s="3"/>
       <c r="K143" s="4"/>
       <c r="L143" s="3"/>
@@ -8355,9 +8562,9 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q143" t="e">
+      <c r="Q143">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="R143" t="e">
         <f t="shared" si="8"/>
@@ -8368,12 +8575,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:19">
       <c r="A144" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B144" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C144">
         <v>0.4</v>
@@ -8413,12 +8620,12 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:19">
       <c r="A145" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B145" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -8452,12 +8659,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:19">
       <c r="A146" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B146" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -8491,12 +8698,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:19">
       <c r="A147" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B147" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -8536,12 +8743,12 @@
         <v>0.94166666666666665</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:19">
       <c r="A148" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B148" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -8581,12 +8788,12 @@
         <v>0.83333333333333326</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:19">
       <c r="A149" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B149" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C149">
         <v>0.4</v>
@@ -8626,12 +8833,12 @@
         <v>0.51666666666666672</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:19">
       <c r="A150" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B150" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8671,22 +8878,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:19">
       <c r="A151" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B151" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C151">
         <v>0.5</v>
       </c>
       <c r="D151" s="1"/>
-      <c r="E151" s="4"/>
+      <c r="E151" s="4">
+        <v>0</v>
+      </c>
       <c r="F151" s="1"/>
-      <c r="G151" s="4"/>
+      <c r="G151" s="4">
+        <v>1</v>
+      </c>
       <c r="H151" s="1"/>
-      <c r="I151" s="4"/>
+      <c r="I151" s="4">
+        <v>1</v>
+      </c>
       <c r="J151" s="1"/>
       <c r="K151" s="4"/>
       <c r="L151" s="1"/>
@@ -8697,9 +8910,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q151" t="e">
+      <c r="Q151">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R151" t="e">
         <f t="shared" si="8"/>
@@ -8710,12 +8923,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:19">
       <c r="A152" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B152" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C152">
         <v>0.5</v>
@@ -8755,12 +8968,12 @@
         <v>0.51666666666666661</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:19">
       <c r="A153" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B153" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C153">
         <v>0.4</v>
@@ -8800,12 +9013,12 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:19">
       <c r="A154" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B154" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -8845,12 +9058,12 @@
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:19">
       <c r="A155" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B155" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C155">
         <v>0.5</v>
@@ -8890,12 +9103,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:19">
       <c r="A156" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B156" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -8935,12 +9148,12 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:19">
       <c r="A157" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B157" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -8974,12 +9187,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:19">
       <c r="A158" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B158" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C158">
         <v>0.4</v>
@@ -9019,12 +9232,12 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:19">
       <c r="A159" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B159" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C159">
         <v>0.5</v>
@@ -9064,12 +9277,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:19">
       <c r="A160" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B160" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -9109,12 +9322,12 @@
         <v>0.76666666666666661</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:19">
       <c r="A161" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B161" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -9154,12 +9367,12 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:19">
       <c r="A162" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B162" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C162">
         <v>0.8</v>
@@ -9199,12 +9412,12 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:19">
       <c r="A163" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B163" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -9244,12 +9457,12 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:19">
       <c r="A164" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B164" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C164">
         <v>0.8</v>
@@ -9289,12 +9502,12 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:19">
       <c r="A165" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B165" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C165">
         <v>0.8</v>
@@ -9334,22 +9547,28 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:19">
       <c r="A166" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B166" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C166">
         <v>0.4</v>
       </c>
       <c r="D166" s="2"/>
-      <c r="E166" s="4"/>
+      <c r="E166" s="4">
+        <v>0</v>
+      </c>
       <c r="F166" s="2"/>
-      <c r="G166" s="4"/>
+      <c r="G166" s="4">
+        <v>1</v>
+      </c>
       <c r="H166" s="2"/>
-      <c r="I166" s="4"/>
+      <c r="I166" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J166" s="2"/>
       <c r="K166" s="4"/>
       <c r="L166" s="2"/>
@@ -9360,9 +9579,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q166" t="e">
+      <c r="Q166">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R166" t="e">
         <f t="shared" si="8"/>
@@ -9373,22 +9592,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:19">
       <c r="A167" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B167" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C167">
         <v>0.4</v>
       </c>
       <c r="D167" s="3"/>
-      <c r="E167" s="4"/>
+      <c r="E167" s="4">
+        <v>1</v>
+      </c>
       <c r="F167" s="3"/>
-      <c r="G167" s="4"/>
+      <c r="G167" s="4">
+        <v>1</v>
+      </c>
       <c r="H167" s="3"/>
-      <c r="I167" s="4"/>
+      <c r="I167" s="4">
+        <v>0</v>
+      </c>
       <c r="J167" s="3"/>
       <c r="K167" s="4"/>
       <c r="L167" s="3"/>
@@ -9399,9 +9624,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q167" t="e">
+      <c r="Q167">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R167" t="e">
         <f t="shared" si="8"/>
@@ -9412,12 +9637,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:19">
       <c r="A168" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B168" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C168">
         <v>0.4</v>
@@ -9457,12 +9682,12 @@
         <v>0.44166666666666665</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:19">
       <c r="A169" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B169" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C169">
         <v>0.5</v>
@@ -9502,12 +9727,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:19">
       <c r="A170" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B170" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C170">
         <v>0.4</v>
@@ -9547,12 +9772,12 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:19">
       <c r="A171" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B171" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -9586,12 +9811,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:19">
       <c r="A172" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B172" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C172">
         <v>0.4</v>
@@ -9631,12 +9856,12 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:19">
       <c r="A173" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B173" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -9670,22 +9895,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:19">
       <c r="A174" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B174" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C174">
         <v>1</v>
       </c>
       <c r="D174" s="1"/>
-      <c r="E174" s="4"/>
+      <c r="E174" s="4">
+        <v>1</v>
+      </c>
       <c r="F174" s="1"/>
-      <c r="G174" s="4"/>
+      <c r="G174" s="4">
+        <v>0</v>
+      </c>
       <c r="H174" s="1"/>
-      <c r="I174" s="4"/>
+      <c r="I174" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J174" s="1"/>
       <c r="K174" s="4"/>
       <c r="L174" s="1"/>
@@ -9696,9 +9927,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q174" t="e">
+      <c r="Q174">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R174" t="e">
         <f t="shared" si="8"/>
@@ -9709,12 +9940,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:19">
       <c r="A175" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B175" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C175">
         <v>0.4</v>
@@ -9748,35 +9979,47 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:19">
       <c r="A176" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B176" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C176">
         <v>0.4</v>
       </c>
       <c r="D176" s="2"/>
-      <c r="E176" s="4"/>
+      <c r="E176" s="4">
+        <v>0</v>
+      </c>
       <c r="F176" s="2"/>
-      <c r="G176" s="4"/>
+      <c r="G176" s="4">
+        <v>0.6</v>
+      </c>
       <c r="H176" s="2"/>
-      <c r="I176" s="4"/>
+      <c r="I176" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J176" s="2"/>
-      <c r="K176" s="4"/>
+      <c r="K176" s="4">
+        <v>1</v>
+      </c>
       <c r="L176" s="2"/>
-      <c r="M176" s="4"/>
+      <c r="M176" s="4">
+        <v>0.3</v>
+      </c>
       <c r="N176" s="2"/>
-      <c r="O176" s="4"/>
+      <c r="O176" s="4">
+        <v>0.3</v>
+      </c>
       <c r="P176" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q176" t="e">
+      <c r="Q176">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.41666666666666657</v>
       </c>
       <c r="R176" t="e">
         <f t="shared" si="8"/>
@@ -9787,22 +10030,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:19">
       <c r="A177" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B177" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C177">
         <v>1</v>
       </c>
       <c r="D177" s="3"/>
-      <c r="E177" s="4"/>
+      <c r="E177" s="4">
+        <v>1</v>
+      </c>
       <c r="F177" s="3"/>
-      <c r="G177" s="4"/>
+      <c r="G177" s="4">
+        <v>0</v>
+      </c>
       <c r="H177" s="3"/>
-      <c r="I177" s="4"/>
+      <c r="I177" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J177" s="3"/>
       <c r="K177" s="4"/>
       <c r="L177" s="3"/>
@@ -9813,9 +10062,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q177" t="e">
+      <c r="Q177">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R177" t="e">
         <f t="shared" si="8"/>
@@ -9826,12 +10075,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:19">
       <c r="A178" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B178" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C178">
         <v>0.4</v>
@@ -9871,12 +10120,12 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:19">
       <c r="A179" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B179" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C179">
         <v>0.4</v>
@@ -9916,12 +10165,12 @@
         <v>0.3666666666666667</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:19">
       <c r="A180" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B180" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C180">
         <v>0.4</v>
@@ -9955,12 +10204,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:19">
       <c r="A181" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B181" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -9994,12 +10243,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:19">
       <c r="A182" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B182" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C182">
         <v>0.4</v>
@@ -10039,12 +10288,12 @@
         <v>0.3666666666666667</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:19">
       <c r="A183" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B183" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C183">
         <v>0.4</v>
@@ -10084,12 +10333,12 @@
         <v>0.39166666666666666</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:19">
       <c r="A184" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B184" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -10129,12 +10378,12 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:19">
       <c r="A185" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B185" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C185">
         <v>0.8</v>
@@ -10174,12 +10423,12 @@
         <v>0.6166666666666667</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:19">
       <c r="A186" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B186" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -10219,12 +10468,12 @@
         <v>0.83333333333333326</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:19">
       <c r="A187" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B187" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -10264,22 +10513,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:19">
       <c r="A188" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B188" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C188">
         <v>0.8</v>
       </c>
       <c r="D188" s="1"/>
-      <c r="E188" s="4"/>
+      <c r="E188" s="4">
+        <v>0.6</v>
+      </c>
       <c r="F188" s="1"/>
-      <c r="G188" s="4"/>
+      <c r="G188" s="4">
+        <v>1</v>
+      </c>
       <c r="H188" s="1"/>
-      <c r="I188" s="4"/>
+      <c r="I188" s="4">
+        <v>1</v>
+      </c>
       <c r="J188" s="1"/>
       <c r="K188" s="4"/>
       <c r="L188" s="1"/>
@@ -10290,9 +10545,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q188" t="e">
+      <c r="Q188">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R188" t="e">
         <f t="shared" si="8"/>
@@ -10303,12 +10558,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:19">
       <c r="A189" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B189" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -10348,12 +10603,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:19">
       <c r="A190" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B190" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -10387,22 +10642,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:19">
       <c r="A191" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B191" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191" s="2"/>
-      <c r="E191" s="4"/>
+      <c r="E191" s="4">
+        <v>1</v>
+      </c>
       <c r="F191" s="2"/>
-      <c r="G191" s="4"/>
+      <c r="G191" s="4">
+        <v>1</v>
+      </c>
       <c r="H191" s="2"/>
-      <c r="I191" s="4"/>
+      <c r="I191" s="4">
+        <v>1</v>
+      </c>
       <c r="J191" s="2"/>
       <c r="K191" s="4"/>
       <c r="L191" s="2"/>
@@ -10413,9 +10674,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q191" t="e">
+      <c r="Q191">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R191" t="e">
         <f t="shared" si="8"/>
@@ -10426,12 +10687,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:19">
       <c r="A192" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B192" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C192">
         <v>0.4</v>
@@ -10471,22 +10732,28 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:19">
       <c r="A193" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B193" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193" s="3"/>
-      <c r="E193" s="4"/>
+      <c r="E193" s="4">
+        <v>1</v>
+      </c>
       <c r="F193" s="3"/>
-      <c r="G193" s="4"/>
+      <c r="G193" s="4">
+        <v>1</v>
+      </c>
       <c r="H193" s="3"/>
-      <c r="I193" s="4"/>
+      <c r="I193" s="4">
+        <v>1</v>
+      </c>
       <c r="J193" s="3"/>
       <c r="K193" s="4"/>
       <c r="L193" s="3"/>
@@ -10497,9 +10764,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q193" t="e">
+      <c r="Q193">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R193" t="e">
         <f t="shared" si="8"/>
@@ -10510,12 +10777,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:19">
       <c r="A194" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B194" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -10555,12 +10822,12 @@
         <v>0.76666666666666661</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:19">
       <c r="A195" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B195" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C195">
         <v>0.5</v>
@@ -10594,12 +10861,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:19">
       <c r="A196" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B196" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -10633,12 +10900,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:19">
       <c r="A197" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B197" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -10696,22 +10963,28 @@
         <v>0.90833333333333321</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:19">
       <c r="A198" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B198" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C198">
         <v>0.2</v>
       </c>
       <c r="D198" s="1"/>
-      <c r="E198" s="4"/>
+      <c r="E198" s="4">
+        <v>0</v>
+      </c>
       <c r="F198" s="1"/>
-      <c r="G198" s="4"/>
+      <c r="G198" s="4">
+        <v>1</v>
+      </c>
       <c r="H198" s="1"/>
-      <c r="I198" s="4"/>
+      <c r="I198" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J198" s="1"/>
       <c r="K198" s="4"/>
       <c r="L198" s="1"/>
@@ -10722,9 +10995,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q198" t="e">
+      <c r="Q198">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="R198" t="e">
         <f t="shared" si="11"/>
@@ -10735,12 +11008,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:19">
       <c r="A199" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B199" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C199">
         <v>0.8</v>
@@ -10774,22 +11047,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:19">
       <c r="A200" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B200" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C200">
         <v>0.8</v>
       </c>
       <c r="D200" s="2"/>
-      <c r="E200" s="4"/>
+      <c r="E200" s="4">
+        <v>0.3</v>
+      </c>
       <c r="F200" s="2"/>
-      <c r="G200" s="4"/>
+      <c r="G200" s="4">
+        <v>1</v>
+      </c>
       <c r="H200" s="2"/>
-      <c r="I200" s="4"/>
+      <c r="I200" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J200" s="2"/>
       <c r="K200" s="4"/>
       <c r="L200" s="2"/>
@@ -10800,9 +11079,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q200" t="e">
+      <c r="Q200">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R200" t="e">
         <f t="shared" si="11"/>
@@ -10813,22 +11092,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:19">
       <c r="A201" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B201" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C201">
         <v>0.8</v>
       </c>
       <c r="D201" s="3"/>
-      <c r="E201" s="4"/>
+      <c r="E201" s="4">
+        <v>0.3</v>
+      </c>
       <c r="F201" s="3"/>
-      <c r="G201" s="4"/>
+      <c r="G201" s="4">
+        <v>1</v>
+      </c>
       <c r="H201" s="3"/>
-      <c r="I201" s="4"/>
+      <c r="I201" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J201" s="3"/>
       <c r="K201" s="4"/>
       <c r="L201" s="3"/>
@@ -10839,9 +11124,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q201" t="e">
+      <c r="Q201">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="R201" t="e">
         <f t="shared" si="11"/>
@@ -10852,12 +11137,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:19">
       <c r="A202" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B202" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -10891,12 +11176,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:19">
       <c r="A203" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B203" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -10930,22 +11215,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:19">
       <c r="A204" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B204" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C204">
         <v>0.2</v>
       </c>
       <c r="D204" s="1"/>
-      <c r="E204" s="4"/>
+      <c r="E204" s="4">
+        <v>1</v>
+      </c>
       <c r="F204" s="1"/>
-      <c r="G204" s="4"/>
+      <c r="G204" s="4">
+        <v>1</v>
+      </c>
       <c r="H204" s="1"/>
-      <c r="I204" s="4"/>
+      <c r="I204" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J204" s="1"/>
       <c r="K204" s="4"/>
       <c r="L204" s="1"/>
@@ -10956,9 +11247,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q204" t="e">
+      <c r="Q204">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R204" t="e">
         <f t="shared" si="11"/>
@@ -10969,12 +11260,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:19">
       <c r="A205" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B205" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C205">
         <v>0.8</v>
@@ -11014,12 +11305,12 @@
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:19">
       <c r="A206" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B206" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C206">
         <v>1</v>
@@ -11077,12 +11368,12 @@
         <v>0.90833333333333321</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:19">
       <c r="A207" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B207" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C207">
         <v>0.2</v>
@@ -11116,22 +11407,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:19">
       <c r="A208" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B208" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C208">
         <v>0.8</v>
       </c>
       <c r="D208" s="2"/>
-      <c r="E208" s="4"/>
+      <c r="E208" s="4">
+        <v>0</v>
+      </c>
       <c r="F208" s="2"/>
-      <c r="G208" s="4"/>
+      <c r="G208" s="4">
+        <v>0</v>
+      </c>
       <c r="H208" s="2"/>
-      <c r="I208" s="4"/>
+      <c r="I208" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J208" s="2"/>
       <c r="K208" s="4"/>
       <c r="L208" s="2"/>
@@ -11142,9 +11439,9 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q208" t="e">
+      <c r="Q208">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="R208" t="e">
         <f t="shared" si="11"/>
@@ -11155,22 +11452,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:19">
       <c r="A209" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B209" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C209">
         <v>0.4</v>
       </c>
       <c r="D209" s="3"/>
-      <c r="E209" s="4"/>
+      <c r="E209" s="4">
+        <v>0</v>
+      </c>
       <c r="F209" s="3"/>
-      <c r="G209" s="4"/>
+      <c r="G209" s="4">
+        <v>1</v>
+      </c>
       <c r="H209" s="3"/>
-      <c r="I209" s="4"/>
+      <c r="I209" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J209" s="3"/>
       <c r="K209" s="4"/>
       <c r="L209" s="3"/>
@@ -11181,9 +11484,9 @@
         <f t="shared" ref="P209:Q272" si="13">AVERAGE(D209,F209,H209,J209,L209,N209)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q209" t="e">
+      <c r="Q209">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="R209" t="e">
         <f t="shared" si="11"/>
@@ -11194,12 +11497,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:19">
       <c r="A210" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B210" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C210">
         <v>0.4</v>
@@ -11233,12 +11536,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:19">
       <c r="A211" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B211" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C211">
         <v>0.4</v>
@@ -11278,12 +11581,12 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:19">
       <c r="A212" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B212" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C212">
         <v>0.5</v>
@@ -11317,12 +11620,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:19">
       <c r="A213" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B213" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C213">
         <v>0.4</v>
@@ -11374,22 +11677,28 @@
         <v>0.29000000000000004</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:19">
       <c r="A214" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B214" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C214">
         <v>0.5</v>
       </c>
       <c r="D214" s="1"/>
-      <c r="E214" s="4"/>
+      <c r="E214" s="4">
+        <v>0</v>
+      </c>
       <c r="F214" s="1"/>
-      <c r="G214" s="4"/>
+      <c r="G214" s="4">
+        <v>1</v>
+      </c>
       <c r="H214" s="1"/>
-      <c r="I214" s="4"/>
+      <c r="I214" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J214" s="1"/>
       <c r="K214" s="4"/>
       <c r="L214" s="1"/>
@@ -11400,9 +11709,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q214" t="e">
+      <c r="Q214">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="R214" t="e">
         <f t="shared" si="11"/>
@@ -11413,12 +11722,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:19">
       <c r="A215" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B215" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C215">
         <v>0.8</v>
@@ -11452,22 +11761,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:19">
       <c r="A216" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B216" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C216">
         <v>0.2</v>
       </c>
       <c r="D216" s="2"/>
-      <c r="E216" s="4"/>
+      <c r="E216" s="4">
+        <v>0</v>
+      </c>
       <c r="F216" s="2"/>
-      <c r="G216" s="4"/>
+      <c r="G216" s="4">
+        <v>1</v>
+      </c>
       <c r="H216" s="2"/>
-      <c r="I216" s="4"/>
+      <c r="I216" s="4">
+        <v>0</v>
+      </c>
       <c r="J216" s="2"/>
       <c r="K216" s="4"/>
       <c r="L216" s="2"/>
@@ -11478,9 +11793,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q216" t="e">
+      <c r="Q216">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="R216" t="e">
         <f t="shared" si="11"/>
@@ -11491,12 +11806,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:19">
       <c r="A217" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B217" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -11536,22 +11851,28 @@
         <v>0.76666666666666661</v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A218" t="s">
-        <v>428</v>
-      </c>
-      <c r="B218" t="s">
-        <v>429</v>
+    <row r="218" spans="1:19">
+      <c r="A218" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>433</v>
       </c>
       <c r="C218">
         <v>0.8</v>
       </c>
       <c r="D218" s="3"/>
-      <c r="E218" s="4"/>
+      <c r="E218" s="4">
+        <v>0.3</v>
+      </c>
       <c r="F218" s="3"/>
-      <c r="G218" s="4"/>
+      <c r="G218" s="4">
+        <v>1</v>
+      </c>
       <c r="H218" s="3"/>
-      <c r="I218" s="4"/>
+      <c r="I218" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J218" s="3"/>
       <c r="K218" s="4"/>
       <c r="L218" s="3"/>
@@ -11562,9 +11883,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q218" t="e">
+      <c r="Q218">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="R218" t="e">
         <f t="shared" si="11"/>
@@ -11575,12 +11896,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:19">
       <c r="A219" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B219" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C219">
         <v>0.4</v>
@@ -11614,12 +11935,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:19">
       <c r="A220" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B220" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -11659,12 +11980,12 @@
         <v>0.7416666666666667</v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:19">
       <c r="A221" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B221" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C221">
         <v>0.8</v>
@@ -11698,12 +12019,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:19">
       <c r="A222" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B222" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C222">
         <v>0.5</v>
@@ -11755,12 +12076,12 @@
         <v>0.60499999999999998</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:19">
       <c r="A223" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B223" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C223">
         <v>0.5</v>
@@ -11800,22 +12121,28 @@
         <v>0.41666666666666663</v>
       </c>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A224" t="s">
-        <v>381</v>
+    <row r="224" spans="1:19">
+      <c r="A224" s="5" t="s">
+        <v>385</v>
       </c>
       <c r="B224" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C224">
         <v>0.8</v>
       </c>
       <c r="D224" s="1"/>
-      <c r="E224" s="4"/>
+      <c r="E224" s="4">
+        <v>0.6</v>
+      </c>
       <c r="F224" s="1"/>
-      <c r="G224" s="4"/>
+      <c r="G224" s="4">
+        <v>1</v>
+      </c>
       <c r="H224" s="1"/>
-      <c r="I224" s="4"/>
+      <c r="I224" s="4">
+        <v>1</v>
+      </c>
       <c r="J224" s="1"/>
       <c r="K224" s="4"/>
       <c r="L224" s="1"/>
@@ -11826,9 +12153,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q224" t="e">
+      <c r="Q224">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R224" t="e">
         <f t="shared" si="11"/>
@@ -11839,12 +12166,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:19">
       <c r="A225" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B225" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C225">
         <v>0.5</v>
@@ -11878,35 +12205,47 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:19">
       <c r="A226" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B226" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C226">
         <v>0.4</v>
       </c>
       <c r="D226" s="2"/>
-      <c r="E226" s="4"/>
+      <c r="E226" s="4">
+        <v>0</v>
+      </c>
       <c r="F226" s="2"/>
-      <c r="G226" s="4"/>
+      <c r="G226" s="4">
+        <v>0.6</v>
+      </c>
       <c r="H226" s="2"/>
-      <c r="I226" s="4"/>
+      <c r="I226" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J226" s="2"/>
-      <c r="K226" s="4"/>
+      <c r="K226" s="4">
+        <v>0.3</v>
+      </c>
       <c r="L226" s="2"/>
-      <c r="M226" s="4"/>
+      <c r="M226" s="4">
+        <v>0.6</v>
+      </c>
       <c r="N226" s="2"/>
-      <c r="O226" s="4"/>
+      <c r="O226" s="4">
+        <v>0.3</v>
+      </c>
       <c r="P226" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q226" t="e">
+      <c r="Q226">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="R226" t="e">
         <f t="shared" si="11"/>
@@ -11917,20 +12256,24 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:19">
       <c r="A227" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B227" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C227">
         <v>0.2</v>
       </c>
       <c r="D227" s="3"/>
-      <c r="E227" s="4"/>
+      <c r="E227" s="4">
+        <v>1</v>
+      </c>
       <c r="F227" s="3"/>
-      <c r="G227" s="4"/>
+      <c r="G227" s="4">
+        <v>1</v>
+      </c>
       <c r="H227" s="3"/>
       <c r="I227" s="4"/>
       <c r="J227" s="3"/>
@@ -11943,9 +12286,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q227" t="e">
+      <c r="Q227">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R227" t="e">
         <f t="shared" si="11"/>
@@ -11956,12 +12299,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:19">
       <c r="A228" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B228" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C228">
         <v>0.4</v>
@@ -12001,12 +12344,12 @@
         <v>0.58333333333333326</v>
       </c>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:19">
       <c r="A229" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B229" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -12040,12 +12383,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:19">
       <c r="A230" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B230" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -12079,12 +12422,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:19">
       <c r="A231" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B231" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C231">
         <v>0.4</v>
@@ -12124,22 +12467,28 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:19">
       <c r="A232" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B232" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C232">
         <v>0.5</v>
       </c>
       <c r="D232" s="1"/>
-      <c r="E232" s="4"/>
+      <c r="E232" s="4">
+        <v>1</v>
+      </c>
       <c r="F232" s="1"/>
-      <c r="G232" s="4"/>
+      <c r="G232" s="4">
+        <v>1</v>
+      </c>
       <c r="H232" s="1"/>
-      <c r="I232" s="4"/>
+      <c r="I232" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J232" s="1"/>
       <c r="K232" s="4"/>
       <c r="L232" s="1"/>
@@ -12150,9 +12499,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q232" t="e">
+      <c r="Q232">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R232" t="e">
         <f t="shared" si="11"/>
@@ -12163,12 +12512,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:19">
       <c r="A233" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B233" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C233">
         <v>0.4</v>
@@ -12208,12 +12557,12 @@
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:19">
       <c r="A234" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B234" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C234">
         <v>0.5</v>
@@ -12253,12 +12602,12 @@
         <v>0.56666666666666665</v>
       </c>
     </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:19">
       <c r="A235" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B235" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C235">
         <v>0.2</v>
@@ -12292,12 +12641,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:19">
       <c r="A236" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B236" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C236">
         <v>0.8</v>
@@ -12337,12 +12686,12 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:19">
       <c r="A237" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B237" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C237">
         <v>0.8</v>
@@ -12382,12 +12731,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:19">
       <c r="A238" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B238" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C238">
         <v>0.4</v>
@@ -12421,9 +12770,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:19">
       <c r="A239" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -12457,19 +12806,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:19">
       <c r="A240" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C240">
         <v>0.4</v>
       </c>
       <c r="D240" s="1"/>
-      <c r="E240" s="4"/>
+      <c r="E240" s="4">
+        <v>1</v>
+      </c>
       <c r="F240" s="1"/>
-      <c r="G240" s="4"/>
+      <c r="G240" s="4">
+        <v>1</v>
+      </c>
       <c r="H240" s="1"/>
-      <c r="I240" s="4"/>
+      <c r="I240" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J240" s="1"/>
       <c r="K240" s="4"/>
       <c r="L240" s="1"/>
@@ -12480,9 +12835,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q240" t="e">
+      <c r="Q240">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="R240" t="e">
         <f t="shared" si="11"/>
@@ -12493,9 +12848,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:19">
       <c r="A241" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -12529,19 +12884,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:19">
       <c r="A242" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C242">
         <v>0.4</v>
       </c>
       <c r="D242" s="2"/>
-      <c r="E242" s="4"/>
+      <c r="E242" s="4">
+        <v>1</v>
+      </c>
       <c r="F242" s="2"/>
-      <c r="G242" s="4"/>
+      <c r="G242" s="4">
+        <v>1</v>
+      </c>
       <c r="H242" s="2"/>
-      <c r="I242" s="4"/>
+      <c r="I242" s="4">
+        <v>1</v>
+      </c>
       <c r="J242" s="2"/>
       <c r="K242" s="4"/>
       <c r="L242" s="2"/>
@@ -12552,9 +12913,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q242" t="e">
+      <c r="Q242">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R242" t="e">
         <f t="shared" si="11"/>
@@ -12565,19 +12926,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:19">
       <c r="A243" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C243">
         <v>1</v>
       </c>
       <c r="D243" s="3"/>
-      <c r="E243" s="4"/>
+      <c r="E243" s="4">
+        <v>1</v>
+      </c>
       <c r="F243" s="3"/>
-      <c r="G243" s="4"/>
+      <c r="G243" s="4">
+        <v>1</v>
+      </c>
       <c r="H243" s="3"/>
-      <c r="I243" s="4"/>
+      <c r="I243" s="4">
+        <v>1</v>
+      </c>
       <c r="J243" s="3"/>
       <c r="K243" s="4"/>
       <c r="L243" s="3"/>
@@ -12588,9 +12955,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q243" t="e">
+      <c r="Q243">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R243" t="e">
         <f t="shared" si="11"/>
@@ -12601,9 +12968,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:19">
       <c r="A244" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -12637,9 +13004,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:19">
       <c r="A245" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C245">
         <v>0.8</v>
@@ -12673,19 +13040,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:19">
       <c r="A246" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C246">
         <v>0.4</v>
       </c>
       <c r="D246" s="1"/>
-      <c r="E246" s="4"/>
+      <c r="E246" s="4">
+        <v>1</v>
+      </c>
       <c r="F246" s="1"/>
-      <c r="G246" s="4"/>
+      <c r="G246" s="4">
+        <v>1</v>
+      </c>
       <c r="H246" s="1"/>
-      <c r="I246" s="4"/>
+      <c r="I246" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J246" s="1"/>
       <c r="K246" s="4"/>
       <c r="L246" s="1"/>
@@ -12696,9 +13069,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q246" t="e">
+      <c r="Q246">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="R246" t="e">
         <f t="shared" si="11"/>
@@ -12709,9 +13082,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:19">
       <c r="A247" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C247">
         <v>0.5</v>
@@ -12745,19 +13118,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:19">
       <c r="A248" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C248">
         <v>0.4</v>
       </c>
       <c r="D248" s="2"/>
-      <c r="E248" s="4"/>
+      <c r="E248" s="4">
+        <v>1</v>
+      </c>
       <c r="F248" s="2"/>
-      <c r="G248" s="4"/>
+      <c r="G248" s="4">
+        <v>1</v>
+      </c>
       <c r="H248" s="2"/>
-      <c r="I248" s="4"/>
+      <c r="I248" s="4">
+        <v>1</v>
+      </c>
       <c r="J248" s="2"/>
       <c r="K248" s="4"/>
       <c r="L248" s="2"/>
@@ -12768,9 +13147,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q248" t="e">
+      <c r="Q248">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R248" t="e">
         <f t="shared" si="11"/>
@@ -12781,19 +13160,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:19">
       <c r="A249" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C249">
         <v>0.4</v>
       </c>
       <c r="D249" s="3"/>
-      <c r="E249" s="4"/>
+      <c r="E249" s="4">
+        <v>0.3</v>
+      </c>
       <c r="F249" s="3"/>
-      <c r="G249" s="4"/>
+      <c r="G249" s="4">
+        <v>1</v>
+      </c>
       <c r="H249" s="3"/>
-      <c r="I249" s="4"/>
+      <c r="I249" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J249" s="3"/>
       <c r="K249" s="4"/>
       <c r="L249" s="3"/>
@@ -12804,9 +13189,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q249" t="e">
+      <c r="Q249">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="R249" t="e">
         <f t="shared" si="11"/>
@@ -12817,9 +13202,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:19">
       <c r="A250" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -12853,9 +13238,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:19">
       <c r="A251" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C251">
         <v>0.4</v>
@@ -12889,19 +13274,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:19">
       <c r="A252" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C252">
         <v>0.8</v>
       </c>
       <c r="D252" s="1"/>
-      <c r="E252" s="4"/>
+      <c r="E252" s="4">
+        <v>1</v>
+      </c>
       <c r="F252" s="1"/>
-      <c r="G252" s="4"/>
+      <c r="G252" s="4">
+        <v>0</v>
+      </c>
       <c r="H252" s="1"/>
-      <c r="I252" s="4"/>
+      <c r="I252" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J252" s="1"/>
       <c r="K252" s="4"/>
       <c r="L252" s="1"/>
@@ -12912,9 +13303,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q252" t="e">
+      <c r="Q252">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R252" t="e">
         <f t="shared" si="11"/>
@@ -12925,9 +13316,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:19">
       <c r="A253" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C253">
         <v>0.4</v>
@@ -12961,19 +13352,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:19">
       <c r="A254" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" s="2"/>
-      <c r="E254" s="4"/>
+      <c r="E254" s="4">
+        <v>1</v>
+      </c>
       <c r="F254" s="2"/>
-      <c r="G254" s="4"/>
+      <c r="G254" s="4">
+        <v>0</v>
+      </c>
       <c r="H254" s="2"/>
-      <c r="I254" s="4"/>
+      <c r="I254" s="4">
+        <v>1</v>
+      </c>
       <c r="J254" s="2"/>
       <c r="K254" s="4"/>
       <c r="L254" s="2"/>
@@ -12984,9 +13381,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q254" t="e">
+      <c r="Q254">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R254" t="e">
         <f t="shared" si="11"/>
@@ -12997,9 +13394,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:19">
       <c r="A255" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C255">
         <v>0.4</v>
@@ -13039,19 +13436,25 @@
         <v>0.55833333333333335</v>
       </c>
     </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:19">
       <c r="A256" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C256">
         <v>0.4</v>
       </c>
       <c r="D256" s="3"/>
-      <c r="E256" s="4"/>
+      <c r="E256" s="4">
+        <v>0</v>
+      </c>
       <c r="F256" s="3"/>
-      <c r="G256" s="4"/>
+      <c r="G256" s="4">
+        <v>1</v>
+      </c>
       <c r="H256" s="3"/>
-      <c r="I256" s="4"/>
+      <c r="I256" s="4">
+        <v>0</v>
+      </c>
       <c r="J256" s="3"/>
       <c r="K256" s="4"/>
       <c r="L256" s="3"/>
@@ -13062,9 +13465,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q256" t="e">
+      <c r="Q256">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="R256" t="e">
         <f t="shared" si="11"/>
@@ -13075,9 +13478,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:19">
       <c r="A257" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C257">
         <v>0.4</v>
@@ -13111,9 +13514,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:19">
       <c r="A258" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C258">
         <v>0.4</v>
@@ -13147,19 +13550,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:19">
       <c r="A259" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C259">
         <v>0.4</v>
       </c>
       <c r="D259" s="1"/>
-      <c r="E259" s="4"/>
+      <c r="E259" s="4">
+        <v>0</v>
+      </c>
       <c r="F259" s="1"/>
-      <c r="G259" s="4"/>
+      <c r="G259" s="4">
+        <v>0</v>
+      </c>
       <c r="H259" s="1"/>
-      <c r="I259" s="4"/>
+      <c r="I259" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J259" s="1"/>
       <c r="K259" s="4"/>
       <c r="L259" s="1"/>
@@ -13170,9 +13579,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q259" t="e">
+      <c r="Q259">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="R259" t="e">
         <f t="shared" ref="R259:R322" si="14">AVERAGE(P259,Q259)</f>
@@ -13183,9 +13592,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:19">
       <c r="A260" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C260">
         <v>0.4</v>
@@ -13219,19 +13628,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:19">
       <c r="A261" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C261">
         <v>0.8</v>
       </c>
       <c r="D261" s="2"/>
-      <c r="E261" s="4"/>
+      <c r="E261" s="4">
+        <v>1</v>
+      </c>
       <c r="F261" s="2"/>
-      <c r="G261" s="4"/>
+      <c r="G261" s="4">
+        <v>0</v>
+      </c>
       <c r="H261" s="2"/>
-      <c r="I261" s="4"/>
+      <c r="I261" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J261" s="2"/>
       <c r="K261" s="4"/>
       <c r="L261" s="2"/>
@@ -13242,9 +13657,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q261" t="e">
+      <c r="Q261">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R261" t="e">
         <f t="shared" si="14"/>
@@ -13255,32 +13670,44 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:19">
       <c r="A262" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C262">
         <v>0.4</v>
       </c>
       <c r="D262" s="3"/>
-      <c r="E262" s="4"/>
+      <c r="E262" s="4">
+        <v>0</v>
+      </c>
       <c r="F262" s="3"/>
-      <c r="G262" s="4"/>
+      <c r="G262" s="4">
+        <v>0.3</v>
+      </c>
       <c r="H262" s="3"/>
-      <c r="I262" s="4"/>
+      <c r="I262" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J262" s="3"/>
-      <c r="K262" s="4"/>
+      <c r="K262" s="4">
+        <v>0.6</v>
+      </c>
       <c r="L262" s="3"/>
-      <c r="M262" s="4"/>
+      <c r="M262" s="4">
+        <v>0.3</v>
+      </c>
       <c r="N262" s="3"/>
-      <c r="O262" s="4"/>
+      <c r="O262" s="4">
+        <v>0.3</v>
+      </c>
       <c r="P262" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q262" t="e">
+      <c r="Q262">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.3</v>
       </c>
       <c r="R262" t="e">
         <f t="shared" si="14"/>
@@ -13291,9 +13718,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:19">
       <c r="A263" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C263">
         <v>0.5</v>
@@ -13327,9 +13754,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:19">
       <c r="A264" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C264">
         <v>0.4</v>
@@ -13363,19 +13790,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:19">
       <c r="A265" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C265">
         <v>0.4</v>
       </c>
       <c r="D265" s="1"/>
-      <c r="E265" s="4"/>
+      <c r="E265" s="4">
+        <v>0</v>
+      </c>
       <c r="F265" s="1"/>
-      <c r="G265" s="4"/>
+      <c r="G265" s="4">
+        <v>1</v>
+      </c>
       <c r="H265" s="1"/>
-      <c r="I265" s="4"/>
+      <c r="I265" s="4">
+        <v>0</v>
+      </c>
       <c r="J265" s="1"/>
       <c r="K265" s="4"/>
       <c r="L265" s="1"/>
@@ -13386,9 +13819,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q265" t="e">
+      <c r="Q265">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="R265" t="e">
         <f t="shared" si="14"/>
@@ -13399,9 +13832,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:19">
       <c r="A266" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C266">
         <v>0.4</v>
@@ -13435,19 +13868,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:19">
       <c r="A267" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C267">
         <v>0.4</v>
       </c>
       <c r="D267" s="2"/>
-      <c r="E267" s="4"/>
+      <c r="E267" s="4">
+        <v>0</v>
+      </c>
       <c r="F267" s="2"/>
-      <c r="G267" s="4"/>
+      <c r="G267" s="4">
+        <v>1</v>
+      </c>
       <c r="H267" s="2"/>
-      <c r="I267" s="4"/>
+      <c r="I267" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J267" s="2"/>
       <c r="K267" s="4"/>
       <c r="L267" s="2"/>
@@ -13458,9 +13897,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q267" t="e">
+      <c r="Q267">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="R267" t="e">
         <f t="shared" si="14"/>
@@ -13471,19 +13910,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:19">
       <c r="A268" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268" s="3"/>
-      <c r="E268" s="4"/>
+      <c r="E268" s="4">
+        <v>1</v>
+      </c>
       <c r="F268" s="3"/>
-      <c r="G268" s="4"/>
+      <c r="G268" s="4">
+        <v>1</v>
+      </c>
       <c r="H268" s="3"/>
-      <c r="I268" s="4"/>
+      <c r="I268" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J268" s="3"/>
       <c r="K268" s="4"/>
       <c r="L268" s="3"/>
@@ -13494,9 +13939,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q268" t="e">
+      <c r="Q268">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R268" t="e">
         <f t="shared" si="14"/>
@@ -13507,9 +13952,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:19">
       <c r="A269" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -13543,9 +13988,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:19">
       <c r="A270" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -13579,19 +14024,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:19">
       <c r="A271" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C271">
         <v>0.4</v>
       </c>
       <c r="D271" s="1"/>
-      <c r="E271" s="4"/>
+      <c r="E271" s="4">
+        <v>1</v>
+      </c>
       <c r="F271" s="1"/>
-      <c r="G271" s="4"/>
+      <c r="G271" s="4">
+        <v>1</v>
+      </c>
       <c r="H271" s="1"/>
-      <c r="I271" s="4"/>
+      <c r="I271" s="4">
+        <v>1</v>
+      </c>
       <c r="J271" s="1"/>
       <c r="K271" s="4"/>
       <c r="L271" s="1"/>
@@ -13602,9 +14053,9 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q271" t="e">
+      <c r="Q271">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R271" t="e">
         <f t="shared" si="14"/>
@@ -13615,9 +14066,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:19">
       <c r="A272" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C272">
         <v>0.4</v>
@@ -13651,19 +14102,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:19">
       <c r="A273" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C273">
         <v>0.5</v>
       </c>
       <c r="D273" s="2"/>
-      <c r="E273" s="4"/>
+      <c r="E273" s="4">
+        <v>1</v>
+      </c>
       <c r="F273" s="2"/>
-      <c r="G273" s="4"/>
+      <c r="G273" s="4">
+        <v>0</v>
+      </c>
       <c r="H273" s="2"/>
-      <c r="I273" s="4"/>
+      <c r="I273" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J273" s="2"/>
       <c r="K273" s="4"/>
       <c r="L273" s="2"/>
@@ -13674,9 +14131,9 @@
         <f t="shared" ref="P273:Q336" si="16">AVERAGE(D273,F273,H273,J273,L273,N273)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q273" t="e">
+      <c r="Q273">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="R273" t="e">
         <f t="shared" si="14"/>
@@ -13687,32 +14144,44 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:19">
       <c r="A274" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C274">
         <v>0.4</v>
       </c>
       <c r="D274" s="3"/>
-      <c r="E274" s="4"/>
+      <c r="E274" s="4">
+        <v>0</v>
+      </c>
       <c r="F274" s="3"/>
-      <c r="G274" s="4"/>
+      <c r="G274" s="4">
+        <v>0.6</v>
+      </c>
       <c r="H274" s="3"/>
-      <c r="I274" s="4"/>
+      <c r="I274" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J274" s="3"/>
-      <c r="K274" s="4"/>
+      <c r="K274" s="4">
+        <v>1</v>
+      </c>
       <c r="L274" s="3"/>
-      <c r="M274" s="4"/>
+      <c r="M274" s="4">
+        <v>0.3</v>
+      </c>
       <c r="N274" s="3"/>
-      <c r="O274" s="4"/>
+      <c r="O274" s="4">
+        <v>0.3</v>
+      </c>
       <c r="P274" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q274" t="e">
+      <c r="Q274">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.46666666666666662</v>
       </c>
       <c r="R274" t="e">
         <f t="shared" si="14"/>
@@ -13723,9 +14192,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:19">
       <c r="A275" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C275">
         <v>0.5</v>
@@ -13759,9 +14228,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:19">
       <c r="A276" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C276">
         <v>0.4</v>
@@ -13795,19 +14264,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:19">
       <c r="A277" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C277">
         <v>0.8</v>
       </c>
       <c r="D277" s="1"/>
-      <c r="E277" s="4"/>
+      <c r="E277" s="4">
+        <v>0.3</v>
+      </c>
       <c r="F277" s="1"/>
-      <c r="G277" s="4"/>
+      <c r="G277" s="4">
+        <v>1</v>
+      </c>
       <c r="H277" s="1"/>
-      <c r="I277" s="4"/>
+      <c r="I277" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J277" s="1"/>
       <c r="K277" s="4"/>
       <c r="L277" s="1"/>
@@ -13818,9 +14293,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q277" t="e">
+      <c r="Q277">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="R277" t="e">
         <f t="shared" si="14"/>
@@ -13831,9 +14306,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:19">
       <c r="A278" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C278">
         <v>0.4</v>
@@ -13867,19 +14342,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A279" t="s">
-        <v>494</v>
+    <row r="279" spans="1:19">
+      <c r="A279" s="6" t="s">
+        <v>498</v>
       </c>
       <c r="C279">
         <v>0.4</v>
       </c>
       <c r="D279" s="2"/>
-      <c r="E279" s="4"/>
+      <c r="E279" s="4">
+        <v>0</v>
+      </c>
       <c r="F279" s="2"/>
-      <c r="G279" s="4"/>
+      <c r="G279" s="4">
+        <v>0</v>
+      </c>
       <c r="H279" s="2"/>
-      <c r="I279" s="4"/>
+      <c r="I279" s="4">
+        <v>0</v>
+      </c>
       <c r="J279" s="2"/>
       <c r="K279" s="4"/>
       <c r="L279" s="2"/>
@@ -13890,9 +14371,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q279" t="e">
+      <c r="Q279">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="R279" t="e">
         <f t="shared" si="14"/>
@@ -13903,19 +14384,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:19">
       <c r="A280" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C280">
         <v>0.4</v>
       </c>
       <c r="D280" s="3"/>
-      <c r="E280" s="4"/>
+      <c r="E280" s="4">
+        <v>1</v>
+      </c>
       <c r="F280" s="3"/>
-      <c r="G280" s="4"/>
+      <c r="G280" s="4">
+        <v>1</v>
+      </c>
       <c r="H280" s="3"/>
-      <c r="I280" s="4"/>
+      <c r="I280" s="4">
+        <v>1</v>
+      </c>
       <c r="J280" s="3"/>
       <c r="K280" s="4"/>
       <c r="L280" s="3"/>
@@ -13926,9 +14413,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q280" t="e">
+      <c r="Q280">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R280" t="e">
         <f t="shared" si="14"/>
@@ -13939,9 +14426,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:19">
       <c r="A281" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C281">
         <v>0.5</v>
@@ -13975,9 +14462,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:19">
       <c r="A282" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C282">
         <v>0.8</v>
@@ -14011,19 +14498,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:19">
       <c r="A283" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C283">
         <v>0.4</v>
       </c>
       <c r="D283" s="1"/>
-      <c r="E283" s="4"/>
+      <c r="E283" s="4">
+        <v>1</v>
+      </c>
       <c r="F283" s="1"/>
-      <c r="G283" s="4"/>
+      <c r="G283" s="4">
+        <v>1</v>
+      </c>
       <c r="H283" s="1"/>
-      <c r="I283" s="4"/>
+      <c r="I283" s="4">
+        <v>1</v>
+      </c>
       <c r="J283" s="1"/>
       <c r="K283" s="4"/>
       <c r="L283" s="1"/>
@@ -14034,9 +14527,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q283" t="e">
+      <c r="Q283">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R283" t="e">
         <f t="shared" si="14"/>
@@ -14047,9 +14540,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:19">
       <c r="A284" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -14083,19 +14576,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:19">
       <c r="A285" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C285">
         <v>0.5</v>
       </c>
       <c r="D285" s="2"/>
-      <c r="E285" s="4"/>
+      <c r="E285" s="4">
+        <v>1</v>
+      </c>
       <c r="F285" s="2"/>
-      <c r="G285" s="4"/>
+      <c r="G285" s="4">
+        <v>1</v>
+      </c>
       <c r="H285" s="2"/>
-      <c r="I285" s="4"/>
+      <c r="I285" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J285" s="2"/>
       <c r="K285" s="4"/>
       <c r="L285" s="2"/>
@@ -14106,9 +14605,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q285" t="e">
+      <c r="Q285">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R285" t="e">
         <f t="shared" si="14"/>
@@ -14119,19 +14618,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:19">
       <c r="A286" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C286">
         <v>0.4</v>
       </c>
       <c r="D286" s="3"/>
-      <c r="E286" s="4"/>
+      <c r="E286" s="4">
+        <v>1</v>
+      </c>
       <c r="F286" s="3"/>
-      <c r="G286" s="4"/>
+      <c r="G286" s="4">
+        <v>1</v>
+      </c>
       <c r="H286" s="3"/>
-      <c r="I286" s="4"/>
+      <c r="I286" s="4">
+        <v>1</v>
+      </c>
       <c r="J286" s="3"/>
       <c r="K286" s="4"/>
       <c r="L286" s="3"/>
@@ -14142,9 +14647,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q286" t="e">
+      <c r="Q286">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R286" t="e">
         <f t="shared" si="14"/>
@@ -14155,9 +14660,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:19">
       <c r="A287" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C287">
         <v>0.5</v>
@@ -14191,9 +14696,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:19">
       <c r="A288" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C288">
         <v>0.8</v>
@@ -14227,19 +14732,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:19">
       <c r="A289" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289" s="1"/>
-      <c r="E289" s="4"/>
+      <c r="E289" s="4">
+        <v>1</v>
+      </c>
       <c r="F289" s="1"/>
-      <c r="G289" s="4"/>
+      <c r="G289" s="4">
+        <v>0</v>
+      </c>
       <c r="H289" s="1"/>
-      <c r="I289" s="4"/>
+      <c r="I289" s="4">
+        <v>1</v>
+      </c>
       <c r="J289" s="1"/>
       <c r="K289" s="4"/>
       <c r="L289" s="1"/>
@@ -14250,9 +14761,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q289" t="e">
+      <c r="Q289">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R289" t="e">
         <f t="shared" si="14"/>
@@ -14263,9 +14774,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:19">
       <c r="A290" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C290">
         <v>0.8</v>
@@ -14299,19 +14810,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:19">
       <c r="A291" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C291">
         <v>0.5</v>
       </c>
       <c r="D291" s="2"/>
-      <c r="E291" s="4"/>
+      <c r="E291" s="4">
+        <v>0</v>
+      </c>
       <c r="F291" s="2"/>
-      <c r="G291" s="4"/>
+      <c r="G291" s="4">
+        <v>0</v>
+      </c>
       <c r="H291" s="2"/>
-      <c r="I291" s="4"/>
+      <c r="I291" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J291" s="2"/>
       <c r="K291" s="4"/>
       <c r="L291" s="2"/>
@@ -14322,9 +14839,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q291" t="e">
+      <c r="Q291">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="R291" t="e">
         <f t="shared" si="14"/>
@@ -14335,19 +14852,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:19">
       <c r="A292" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C292">
         <v>0.4</v>
       </c>
       <c r="D292" s="3"/>
-      <c r="E292" s="4"/>
+      <c r="E292" s="4">
+        <v>0</v>
+      </c>
       <c r="F292" s="3"/>
-      <c r="G292" s="4"/>
+      <c r="G292" s="4">
+        <v>1</v>
+      </c>
       <c r="H292" s="3"/>
-      <c r="I292" s="4"/>
+      <c r="I292" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J292" s="3"/>
       <c r="K292" s="4"/>
       <c r="L292" s="3"/>
@@ -14358,9 +14881,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q292" t="e">
+      <c r="Q292">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R292" t="e">
         <f t="shared" si="14"/>
@@ -14371,9 +14894,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="293" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:19">
       <c r="A293" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C293">
         <v>0.5</v>
@@ -14407,9 +14930,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="294" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:19">
       <c r="A294" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C294">
         <v>0.2</v>
@@ -14443,19 +14966,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="295" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:19">
       <c r="A295" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C295">
         <v>0.4</v>
       </c>
       <c r="D295" s="1"/>
-      <c r="E295" s="4"/>
+      <c r="E295" s="4">
+        <v>1</v>
+      </c>
       <c r="F295" s="1"/>
-      <c r="G295" s="4"/>
+      <c r="G295" s="4">
+        <v>0</v>
+      </c>
       <c r="H295" s="1"/>
-      <c r="I295" s="4"/>
+      <c r="I295" s="4">
+        <v>0</v>
+      </c>
       <c r="J295" s="1"/>
       <c r="K295" s="4"/>
       <c r="L295" s="1"/>
@@ -14466,9 +14995,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q295" t="e">
+      <c r="Q295">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="R295" t="e">
         <f t="shared" si="14"/>
@@ -14479,9 +15008,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="296" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:19">
       <c r="A296" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C296">
         <v>0.4</v>
@@ -14515,19 +15044,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="297" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:19">
       <c r="A297" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C297">
         <v>0.4</v>
       </c>
       <c r="D297" s="2"/>
-      <c r="E297" s="4"/>
+      <c r="E297" s="4">
+        <v>1</v>
+      </c>
       <c r="F297" s="2"/>
-      <c r="G297" s="4"/>
+      <c r="G297" s="4">
+        <v>1</v>
+      </c>
       <c r="H297" s="2"/>
-      <c r="I297" s="4"/>
+      <c r="I297" s="4">
+        <v>0</v>
+      </c>
       <c r="J297" s="2"/>
       <c r="K297" s="4"/>
       <c r="L297" s="2"/>
@@ -14538,9 +15073,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q297" t="e">
+      <c r="Q297">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R297" t="e">
         <f t="shared" si="14"/>
@@ -14551,19 +15086,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="298" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:19">
       <c r="A298" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C298">
         <v>0.5</v>
       </c>
       <c r="D298" s="3"/>
-      <c r="E298" s="4"/>
+      <c r="E298" s="4">
+        <v>1</v>
+      </c>
       <c r="F298" s="3"/>
-      <c r="G298" s="4"/>
+      <c r="G298" s="4">
+        <v>1</v>
+      </c>
       <c r="H298" s="3"/>
-      <c r="I298" s="4"/>
+      <c r="I298" s="4">
+        <v>1</v>
+      </c>
       <c r="J298" s="3"/>
       <c r="K298" s="4"/>
       <c r="L298" s="3"/>
@@ -14574,9 +15115,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q298" t="e">
+      <c r="Q298">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R298" t="e">
         <f t="shared" si="14"/>
@@ -14587,9 +15128,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:19">
       <c r="A299" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C299">
         <v>0.4</v>
@@ -14623,9 +15164,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:19">
       <c r="A300" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C300">
         <v>0.5</v>
@@ -14659,19 +15200,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:19">
       <c r="A301" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C301">
         <v>0.4</v>
       </c>
       <c r="D301" s="1"/>
-      <c r="E301" s="4"/>
+      <c r="E301" s="4">
+        <v>0.6</v>
+      </c>
       <c r="F301" s="1"/>
-      <c r="G301" s="4"/>
+      <c r="G301" s="4">
+        <v>1</v>
+      </c>
       <c r="H301" s="1"/>
-      <c r="I301" s="4"/>
+      <c r="I301" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J301" s="1"/>
       <c r="K301" s="4"/>
       <c r="L301" s="1"/>
@@ -14682,9 +15229,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q301" t="e">
+      <c r="Q301">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.73333333333333339</v>
       </c>
       <c r="R301" t="e">
         <f t="shared" si="14"/>
@@ -14695,9 +15242,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="302" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:19">
       <c r="A302" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C302">
         <v>0.4</v>
@@ -14731,19 +15278,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="303" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:19">
       <c r="A303" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C303">
         <v>0.4</v>
       </c>
       <c r="D303" s="2"/>
-      <c r="E303" s="4"/>
+      <c r="E303" s="4">
+        <v>0</v>
+      </c>
       <c r="F303" s="2"/>
-      <c r="G303" s="4"/>
+      <c r="G303" s="4">
+        <v>1</v>
+      </c>
       <c r="H303" s="2"/>
-      <c r="I303" s="4"/>
+      <c r="I303" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J303" s="2"/>
       <c r="K303" s="4"/>
       <c r="L303" s="2"/>
@@ -14754,9 +15307,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q303" t="e">
+      <c r="Q303">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R303" t="e">
         <f t="shared" si="14"/>
@@ -14767,19 +15320,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="304" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:19">
       <c r="A304" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C304">
         <v>0.4</v>
       </c>
       <c r="D304" s="3"/>
-      <c r="E304" s="4"/>
+      <c r="E304" s="4">
+        <v>1</v>
+      </c>
       <c r="F304" s="3"/>
-      <c r="G304" s="4"/>
+      <c r="G304" s="4">
+        <v>1</v>
+      </c>
       <c r="H304" s="3"/>
-      <c r="I304" s="4"/>
+      <c r="I304" s="4">
+        <v>0</v>
+      </c>
       <c r="J304" s="3"/>
       <c r="K304" s="4"/>
       <c r="L304" s="3"/>
@@ -14790,9 +15349,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q304" t="e">
+      <c r="Q304">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R304" t="e">
         <f t="shared" si="14"/>
@@ -14803,9 +15362,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="305" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:19">
       <c r="A305" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C305">
         <v>0.4</v>
@@ -14839,9 +15398,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="306" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:19">
       <c r="A306" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C306">
         <v>0.4</v>
@@ -14875,32 +15434,44 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:19">
       <c r="A307" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C307">
         <v>0.2</v>
       </c>
       <c r="D307" s="1"/>
-      <c r="E307" s="4"/>
+      <c r="E307" s="4">
+        <v>1</v>
+      </c>
       <c r="F307" s="1"/>
-      <c r="G307" s="4"/>
+      <c r="G307" s="4">
+        <v>1</v>
+      </c>
       <c r="H307" s="1"/>
-      <c r="I307" s="4"/>
+      <c r="I307" s="4">
+        <v>1</v>
+      </c>
       <c r="J307" s="1"/>
-      <c r="K307" s="4"/>
+      <c r="K307" s="4">
+        <v>1</v>
+      </c>
       <c r="L307" s="1"/>
-      <c r="M307" s="4"/>
+      <c r="M307" s="4">
+        <v>0.6</v>
+      </c>
       <c r="N307" s="1"/>
-      <c r="O307" s="4"/>
+      <c r="O307" s="4">
+        <v>1</v>
+      </c>
       <c r="P307" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q307" t="e">
+      <c r="Q307">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.93333333333333324</v>
       </c>
       <c r="R307" t="e">
         <f t="shared" si="14"/>
@@ -14911,9 +15482,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="308" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:19">
       <c r="A308" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C308">
         <v>0.4</v>
@@ -14947,19 +15518,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="309" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:19">
       <c r="A309" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C309">
         <v>0.4</v>
       </c>
       <c r="D309" s="2"/>
-      <c r="E309" s="4"/>
+      <c r="E309" s="4">
+        <v>1</v>
+      </c>
       <c r="F309" s="2"/>
-      <c r="G309" s="4"/>
+      <c r="G309" s="4">
+        <v>1</v>
+      </c>
       <c r="H309" s="2"/>
-      <c r="I309" s="4"/>
+      <c r="I309" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J309" s="2"/>
       <c r="K309" s="4"/>
       <c r="L309" s="2"/>
@@ -14970,9 +15547,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q309" t="e">
+      <c r="Q309">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="R309" t="e">
         <f t="shared" si="14"/>
@@ -14983,19 +15560,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="310" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:19">
       <c r="A310" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C310">
         <v>0.4</v>
       </c>
       <c r="D310" s="3"/>
-      <c r="E310" s="4"/>
+      <c r="E310" s="4">
+        <v>1</v>
+      </c>
       <c r="F310" s="3"/>
-      <c r="G310" s="4"/>
+      <c r="G310" s="4">
+        <v>1</v>
+      </c>
       <c r="H310" s="3"/>
-      <c r="I310" s="4"/>
+      <c r="I310" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J310" s="3"/>
       <c r="K310" s="4"/>
       <c r="L310" s="3"/>
@@ -15006,9 +15589,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q310" t="e">
+      <c r="Q310">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R310" t="e">
         <f t="shared" si="14"/>
@@ -15019,9 +15602,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="311" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:19">
       <c r="A311" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C311">
         <v>0.2</v>
@@ -15055,9 +15638,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="312" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:19">
       <c r="A312" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C312">
         <v>0.4</v>
@@ -15091,19 +15674,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:19">
       <c r="A313" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C313">
         <v>1</v>
       </c>
       <c r="D313" s="1"/>
-      <c r="E313" s="4"/>
+      <c r="E313" s="4">
+        <v>1</v>
+      </c>
       <c r="F313" s="1"/>
-      <c r="G313" s="4"/>
+      <c r="G313" s="4">
+        <v>0</v>
+      </c>
       <c r="H313" s="1"/>
-      <c r="I313" s="4"/>
+      <c r="I313" s="4">
+        <v>1</v>
+      </c>
       <c r="J313" s="1"/>
       <c r="K313" s="4"/>
       <c r="L313" s="1"/>
@@ -15114,9 +15703,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q313" t="e">
+      <c r="Q313">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R313" t="e">
         <f t="shared" si="14"/>
@@ -15127,9 +15716,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="314" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:19">
       <c r="A314" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C314">
         <v>0.5</v>
@@ -15163,19 +15752,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="315" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:19">
       <c r="A315" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C315">
         <v>0.5</v>
       </c>
       <c r="D315" s="2"/>
-      <c r="E315" s="4"/>
+      <c r="E315" s="4">
+        <v>0</v>
+      </c>
       <c r="F315" s="2"/>
-      <c r="G315" s="4"/>
+      <c r="G315" s="4">
+        <v>1</v>
+      </c>
       <c r="H315" s="2"/>
-      <c r="I315" s="4"/>
+      <c r="I315" s="4">
+        <v>0</v>
+      </c>
       <c r="J315" s="2"/>
       <c r="K315" s="4"/>
       <c r="L315" s="2"/>
@@ -15186,9 +15781,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q315" t="e">
+      <c r="Q315">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="R315" t="e">
         <f t="shared" si="14"/>
@@ -15199,9 +15794,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="316" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:19">
       <c r="A316" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C316">
         <v>0.5</v>
@@ -15235,9 +15830,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="317" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:19">
       <c r="A317" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -15271,9 +15866,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="318" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:19">
       <c r="A318" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C318">
         <v>0.4</v>
@@ -15307,19 +15902,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="319" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:19">
       <c r="A319" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C319">
         <v>1</v>
       </c>
       <c r="D319" s="1"/>
-      <c r="E319" s="4"/>
+      <c r="E319" s="4">
+        <v>1</v>
+      </c>
       <c r="F319" s="1"/>
-      <c r="G319" s="4"/>
+      <c r="G319" s="4">
+        <v>0</v>
+      </c>
       <c r="H319" s="1"/>
-      <c r="I319" s="4"/>
+      <c r="I319" s="4">
+        <v>1</v>
+      </c>
       <c r="J319" s="1"/>
       <c r="K319" s="4"/>
       <c r="L319" s="1"/>
@@ -15330,9 +15931,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q319" t="e">
+      <c r="Q319">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R319" t="e">
         <f t="shared" si="14"/>
@@ -15343,9 +15944,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="320" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:19">
       <c r="A320" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C320">
         <v>0.4</v>
@@ -15379,19 +15980,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="321" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:19">
       <c r="A321" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C321">
         <v>0.5</v>
       </c>
       <c r="D321" s="2"/>
-      <c r="E321" s="4"/>
+      <c r="E321" s="4">
+        <v>1</v>
+      </c>
       <c r="F321" s="2"/>
-      <c r="G321" s="4"/>
+      <c r="G321" s="4">
+        <v>1</v>
+      </c>
       <c r="H321" s="2"/>
-      <c r="I321" s="4"/>
+      <c r="I321" s="4">
+        <v>1</v>
+      </c>
       <c r="J321" s="2"/>
       <c r="K321" s="4"/>
       <c r="L321" s="2"/>
@@ -15402,9 +16009,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q321" t="e">
+      <c r="Q321">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R321" t="e">
         <f t="shared" si="14"/>
@@ -15415,9 +16022,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="322" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:19">
       <c r="A322" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C322">
         <v>0.5</v>
@@ -15457,9 +16064,9 @@
         <v>0.60833333333333328</v>
       </c>
     </row>
-    <row r="323" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:19">
       <c r="A323" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C323">
         <v>0.5</v>
@@ -15493,9 +16100,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="324" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:19">
       <c r="A324" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -15529,19 +16136,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="325" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:19">
       <c r="A325" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C325">
         <v>0.4</v>
       </c>
       <c r="D325" s="1"/>
-      <c r="E325" s="4"/>
+      <c r="E325" s="4">
+        <v>1</v>
+      </c>
       <c r="F325" s="1"/>
-      <c r="G325" s="4"/>
+      <c r="G325" s="4">
+        <v>0</v>
+      </c>
       <c r="H325" s="1"/>
-      <c r="I325" s="4"/>
+      <c r="I325" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J325" s="1"/>
       <c r="K325" s="4"/>
       <c r="L325" s="1"/>
@@ -15552,9 +16165,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q325" t="e">
+      <c r="Q325">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R325" t="e">
         <f t="shared" si="17"/>
@@ -15565,9 +16178,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="326" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:19">
       <c r="A326" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C326">
         <v>0.8</v>
@@ -15601,19 +16214,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="327" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:19">
       <c r="A327" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C327">
         <v>0.2</v>
       </c>
       <c r="D327" s="2"/>
-      <c r="E327" s="4"/>
+      <c r="E327" s="4">
+        <v>0</v>
+      </c>
       <c r="F327" s="2"/>
-      <c r="G327" s="4"/>
+      <c r="G327" s="4">
+        <v>1</v>
+      </c>
       <c r="H327" s="2"/>
-      <c r="I327" s="4"/>
+      <c r="I327" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J327" s="2"/>
       <c r="K327" s="4"/>
       <c r="L327" s="2"/>
@@ -15624,9 +16243,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q327" t="e">
+      <c r="Q327">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R327" t="e">
         <f t="shared" si="17"/>
@@ -15637,19 +16256,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="328" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:19">
       <c r="A328" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C328">
         <v>0.4</v>
       </c>
       <c r="D328" s="3"/>
-      <c r="E328" s="4"/>
+      <c r="E328" s="4">
+        <v>0.3</v>
+      </c>
       <c r="F328" s="3"/>
-      <c r="G328" s="4"/>
+      <c r="G328" s="4">
+        <v>1</v>
+      </c>
       <c r="H328" s="3"/>
-      <c r="I328" s="4"/>
+      <c r="I328" s="4">
+        <v>0</v>
+      </c>
       <c r="J328" s="3"/>
       <c r="K328" s="4"/>
       <c r="L328" s="3"/>
@@ -15660,9 +16285,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q328" t="e">
+      <c r="Q328">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="R328" t="e">
         <f t="shared" si="17"/>
@@ -15673,9 +16298,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="329" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:19">
       <c r="A329" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C329">
         <v>0.5</v>
@@ -15709,9 +16334,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="330" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:19">
       <c r="A330" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C330">
         <v>0.4</v>
@@ -15745,19 +16370,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="331" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:19">
       <c r="A331" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C331">
         <v>0.4</v>
       </c>
       <c r="D331" s="1"/>
-      <c r="E331" s="4"/>
+      <c r="E331" s="4">
+        <v>1</v>
+      </c>
       <c r="F331" s="1"/>
-      <c r="G331" s="4"/>
+      <c r="G331" s="4">
+        <v>1</v>
+      </c>
       <c r="H331" s="1"/>
-      <c r="I331" s="4"/>
+      <c r="I331" s="4">
+        <v>0</v>
+      </c>
       <c r="J331" s="1"/>
       <c r="K331" s="4"/>
       <c r="L331" s="1"/>
@@ -15768,9 +16399,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q331" t="e">
+      <c r="Q331">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R331" t="e">
         <f t="shared" si="17"/>
@@ -15781,9 +16412,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="332" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:19">
       <c r="A332" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C332">
         <v>0.5</v>
@@ -15817,19 +16448,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="333" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:19">
       <c r="A333" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C333">
         <v>1</v>
       </c>
       <c r="D333" s="2"/>
-      <c r="E333" s="4"/>
+      <c r="E333" s="4">
+        <v>1</v>
+      </c>
       <c r="F333" s="2"/>
-      <c r="G333" s="4"/>
+      <c r="G333" s="4">
+        <v>1</v>
+      </c>
       <c r="H333" s="2"/>
-      <c r="I333" s="4"/>
+      <c r="I333" s="4">
+        <v>0</v>
+      </c>
       <c r="J333" s="2"/>
       <c r="K333" s="4"/>
       <c r="L333" s="2"/>
@@ -15840,9 +16477,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q333" t="e">
+      <c r="Q333">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R333" t="e">
         <f t="shared" si="17"/>
@@ -15853,19 +16490,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="334" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:19">
       <c r="A334" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C334">
         <v>0.4</v>
       </c>
       <c r="D334" s="3"/>
-      <c r="E334" s="4"/>
+      <c r="E334" s="4">
+        <v>0</v>
+      </c>
       <c r="F334" s="3"/>
-      <c r="G334" s="4"/>
+      <c r="G334" s="4">
+        <v>0</v>
+      </c>
       <c r="H334" s="3"/>
-      <c r="I334" s="4"/>
+      <c r="I334" s="4">
+        <v>0</v>
+      </c>
       <c r="J334" s="3"/>
       <c r="K334" s="4"/>
       <c r="L334" s="3"/>
@@ -15876,9 +16519,9 @@
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q334" t="e">
+      <c r="Q334">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="R334" t="e">
         <f t="shared" si="17"/>
@@ -15889,9 +16532,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="335" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:19">
       <c r="A335" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -15925,9 +16568,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="336" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:19">
       <c r="A336" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C336">
         <v>0.5</v>
@@ -15961,19 +16604,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="337" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:19">
       <c r="A337" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C337">
         <v>0.4</v>
       </c>
       <c r="D337" s="1"/>
-      <c r="E337" s="4"/>
+      <c r="E337" s="4">
+        <v>1</v>
+      </c>
       <c r="F337" s="1"/>
-      <c r="G337" s="4"/>
+      <c r="G337" s="4">
+        <v>1</v>
+      </c>
       <c r="H337" s="1"/>
-      <c r="I337" s="4"/>
+      <c r="I337" s="4">
+        <v>0</v>
+      </c>
       <c r="J337" s="1"/>
       <c r="K337" s="4"/>
       <c r="L337" s="1"/>
@@ -15984,9 +16633,9 @@
         <f t="shared" ref="P337:Q365" si="19">AVERAGE(D337,F337,H337,J337,L337,N337)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q337" t="e">
+      <c r="Q337">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R337" t="e">
         <f t="shared" si="17"/>
@@ -15997,9 +16646,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:19">
       <c r="A338" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C338">
         <v>0.5</v>
@@ -16033,19 +16682,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:19">
       <c r="A339" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C339">
         <v>1</v>
       </c>
       <c r="D339" s="2"/>
-      <c r="E339" s="4"/>
+      <c r="E339" s="4">
+        <v>1</v>
+      </c>
       <c r="F339" s="2"/>
-      <c r="G339" s="4"/>
+      <c r="G339" s="4">
+        <v>1</v>
+      </c>
       <c r="H339" s="2"/>
-      <c r="I339" s="4"/>
+      <c r="I339" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J339" s="2"/>
       <c r="K339" s="4"/>
       <c r="L339" s="2"/>
@@ -16056,9 +16711,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q339" t="e">
+      <c r="Q339">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R339" t="e">
         <f t="shared" si="17"/>
@@ -16069,19 +16724,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="340" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:19">
       <c r="A340" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C340">
         <v>0.5</v>
       </c>
       <c r="D340" s="3"/>
-      <c r="E340" s="4"/>
+      <c r="E340" s="4">
+        <v>1</v>
+      </c>
       <c r="F340" s="3"/>
-      <c r="G340" s="4"/>
+      <c r="G340" s="4">
+        <v>1</v>
+      </c>
       <c r="H340" s="3"/>
-      <c r="I340" s="4"/>
+      <c r="I340" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J340" s="3"/>
       <c r="K340" s="4"/>
       <c r="L340" s="3"/>
@@ -16092,9 +16753,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q340" t="e">
+      <c r="Q340">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R340" t="e">
         <f t="shared" si="17"/>
@@ -16105,9 +16766,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:19">
       <c r="A341" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C341">
         <v>0.8</v>
@@ -16141,9 +16802,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="342" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:19">
       <c r="A342" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -16177,15 +16838,17 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="343" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:19">
       <c r="A343" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C343">
         <v>0.2</v>
       </c>
       <c r="D343" s="1"/>
-      <c r="E343" s="4"/>
+      <c r="E343" s="4">
+        <v>1</v>
+      </c>
       <c r="F343" s="1"/>
       <c r="G343" s="4"/>
       <c r="H343" s="1"/>
@@ -16200,9 +16863,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q343" t="e">
+      <c r="Q343">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R343" t="e">
         <f t="shared" si="17"/>
@@ -16213,9 +16876,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="344" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:19">
       <c r="A344" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C344">
         <v>0.4</v>
@@ -16249,19 +16912,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="345" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:19">
       <c r="A345" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C345">
         <v>0.4</v>
       </c>
       <c r="D345" s="2"/>
-      <c r="E345" s="4"/>
+      <c r="E345" s="4">
+        <v>1</v>
+      </c>
       <c r="F345" s="2"/>
-      <c r="G345" s="4"/>
+      <c r="G345" s="4">
+        <v>1</v>
+      </c>
       <c r="H345" s="2"/>
-      <c r="I345" s="4"/>
+      <c r="I345" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J345" s="2"/>
       <c r="K345" s="4"/>
       <c r="L345" s="2"/>
@@ -16272,9 +16941,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q345" t="e">
+      <c r="Q345">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R345" t="e">
         <f t="shared" si="17"/>
@@ -16285,9 +16954,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:19">
       <c r="A346" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C346">
         <v>0.8</v>
@@ -16327,19 +16996,25 @@
         <v>0.7583333333333333</v>
       </c>
     </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:19">
       <c r="A347" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C347">
         <v>0.5</v>
       </c>
       <c r="D347" s="3"/>
-      <c r="E347" s="4"/>
+      <c r="E347" s="4">
+        <v>0</v>
+      </c>
       <c r="F347" s="3"/>
-      <c r="G347" s="4"/>
+      <c r="G347" s="4">
+        <v>1</v>
+      </c>
       <c r="H347" s="3"/>
-      <c r="I347" s="4"/>
+      <c r="I347" s="4">
+        <v>1</v>
+      </c>
       <c r="J347" s="3"/>
       <c r="K347" s="4"/>
       <c r="L347" s="3"/>
@@ -16350,9 +17025,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q347" t="e">
+      <c r="Q347">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R347" t="e">
         <f t="shared" si="17"/>
@@ -16363,9 +17038,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:19">
       <c r="A348" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -16399,9 +17074,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:19">
       <c r="A349" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -16435,19 +17110,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:19">
       <c r="A350" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C350">
         <v>0.2</v>
       </c>
       <c r="D350" s="1"/>
-      <c r="E350" s="4"/>
+      <c r="E350" s="4">
+        <v>1</v>
+      </c>
       <c r="F350" s="1"/>
-      <c r="G350" s="4"/>
+      <c r="G350" s="4">
+        <v>0</v>
+      </c>
       <c r="H350" s="1"/>
-      <c r="I350" s="4"/>
+      <c r="I350" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J350" s="1"/>
       <c r="K350" s="4"/>
       <c r="L350" s="1"/>
@@ -16458,9 +17139,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q350" t="e">
+      <c r="Q350">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="R350" t="e">
         <f t="shared" si="17"/>
@@ -16471,9 +17152,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:19">
       <c r="A351" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C351">
         <v>0.2</v>
@@ -16507,15 +17188,17 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:19">
       <c r="A352" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C352">
         <v>0.2</v>
       </c>
       <c r="D352" s="2"/>
-      <c r="E352" s="4"/>
+      <c r="E352" s="4">
+        <v>1</v>
+      </c>
       <c r="F352" s="2"/>
       <c r="G352" s="4"/>
       <c r="H352" s="2"/>
@@ -16530,9 +17213,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q352" t="e">
+      <c r="Q352">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R352" t="e">
         <f t="shared" si="17"/>
@@ -16543,9 +17226,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:19">
       <c r="A353" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C353">
         <v>0.4</v>
@@ -16585,19 +17268,25 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="354" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:19">
       <c r="A354" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C354">
         <v>1</v>
       </c>
       <c r="D354" s="3"/>
-      <c r="E354" s="4"/>
+      <c r="E354" s="4">
+        <v>1</v>
+      </c>
       <c r="F354" s="3"/>
-      <c r="G354" s="4"/>
+      <c r="G354" s="4">
+        <v>1</v>
+      </c>
       <c r="H354" s="3"/>
-      <c r="I354" s="4"/>
+      <c r="I354" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J354" s="3"/>
       <c r="K354" s="4"/>
       <c r="L354" s="3"/>
@@ -16608,9 +17297,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q354" t="e">
+      <c r="Q354">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R354" t="e">
         <f t="shared" si="17"/>
@@ -16621,9 +17310,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="355" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:19">
       <c r="A355" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C355">
         <v>0.8</v>
@@ -16657,9 +17346,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:19">
       <c r="A356" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C356">
         <v>0.4</v>
@@ -16693,19 +17382,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:19">
       <c r="A357" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C357">
         <v>1</v>
       </c>
       <c r="D357" s="1"/>
-      <c r="E357" s="4"/>
+      <c r="E357" s="4">
+        <v>1</v>
+      </c>
       <c r="F357" s="1"/>
-      <c r="G357" s="4"/>
+      <c r="G357" s="4">
+        <v>0</v>
+      </c>
       <c r="H357" s="1"/>
-      <c r="I357" s="4"/>
+      <c r="I357" s="4">
+        <v>1</v>
+      </c>
       <c r="J357" s="1"/>
       <c r="K357" s="4"/>
       <c r="L357" s="1"/>
@@ -16716,9 +17411,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q357" t="e">
+      <c r="Q357">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R357" t="e">
         <f t="shared" si="17"/>
@@ -16729,9 +17424,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:19">
       <c r="A358" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C358">
         <v>0.4</v>
@@ -16765,19 +17460,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:19">
       <c r="A359" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C359">
         <v>0.4</v>
       </c>
       <c r="D359" s="2"/>
-      <c r="E359" s="4"/>
+      <c r="E359" s="4">
+        <v>0</v>
+      </c>
       <c r="F359" s="2"/>
-      <c r="G359" s="4"/>
+      <c r="G359" s="4">
+        <v>0</v>
+      </c>
       <c r="H359" s="2"/>
-      <c r="I359" s="4"/>
+      <c r="I359" s="4">
+        <v>1</v>
+      </c>
       <c r="J359" s="2"/>
       <c r="K359" s="4"/>
       <c r="L359" s="2"/>
@@ -16788,9 +17489,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q359" t="e">
+      <c r="Q359">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="R359" t="e">
         <f t="shared" si="17"/>
@@ -16801,19 +17502,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="360" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:19">
       <c r="A360" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C360">
         <v>0.4</v>
       </c>
       <c r="D360" s="3"/>
-      <c r="E360" s="4"/>
+      <c r="E360" s="4">
+        <v>1</v>
+      </c>
       <c r="F360" s="3"/>
-      <c r="G360" s="4"/>
+      <c r="G360" s="4">
+        <v>1</v>
+      </c>
       <c r="H360" s="3"/>
-      <c r="I360" s="4"/>
+      <c r="I360" s="4">
+        <v>1</v>
+      </c>
       <c r="J360" s="3"/>
       <c r="K360" s="4"/>
       <c r="L360" s="3"/>
@@ -16824,9 +17531,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q360" t="e">
+      <c r="Q360">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="R360" t="e">
         <f t="shared" si="17"/>
@@ -16837,9 +17544,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:19">
       <c r="A361" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C361">
         <v>0.4</v>
@@ -16873,9 +17580,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:19">
       <c r="A362" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C362">
         <v>0.4</v>
@@ -16909,19 +17616,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:19">
       <c r="A363" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C363">
         <v>0.4</v>
       </c>
       <c r="D363" s="1"/>
-      <c r="E363" s="4"/>
+      <c r="E363" s="4">
+        <v>0.3</v>
+      </c>
       <c r="F363" s="1"/>
-      <c r="G363" s="4"/>
+      <c r="G363" s="4">
+        <v>0</v>
+      </c>
       <c r="H363" s="1"/>
-      <c r="I363" s="4"/>
+      <c r="I363" s="4">
+        <v>0.3</v>
+      </c>
       <c r="J363" s="1"/>
       <c r="K363" s="4"/>
       <c r="L363" s="1"/>
@@ -16932,9 +17645,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q363" t="e">
+      <c r="Q363">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="R363" t="e">
         <f t="shared" si="17"/>
@@ -16945,9 +17658,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:19">
       <c r="A364" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C364">
         <v>0.4</v>
@@ -16981,19 +17694,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:19">
       <c r="A365" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C365">
         <v>0.5</v>
       </c>
       <c r="D365" s="2"/>
-      <c r="E365" s="4"/>
+      <c r="E365" s="4">
+        <v>1</v>
+      </c>
       <c r="F365" s="2"/>
-      <c r="G365" s="4"/>
+      <c r="G365" s="4">
+        <v>1</v>
+      </c>
       <c r="H365" s="2"/>
-      <c r="I365" s="4"/>
+      <c r="I365" s="4">
+        <v>0.6</v>
+      </c>
       <c r="J365" s="2"/>
       <c r="K365" s="4"/>
       <c r="L365" s="2"/>
@@ -17004,9 +17723,9 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q365" t="e">
+      <c r="Q365">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="R365" t="e">
         <f t="shared" si="17"/>
@@ -17020,4 +17739,231 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6889C2593FACB4192549183B8B19287" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d0441ed93293d98676a3ed4ecc34a2e8">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ab92c565-5003-4ac3-93a3-a3ce8796a3c0" xmlns:ns3="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="338d4716adf2f542ea7f86f5cbff3681" ns2:_="" ns3:_="">
+    <xsd:import namespace="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
+    <xsd:import namespace="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ab92c565-5003-4ac3-93a3-a3ce8796a3c0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="75195dc1-fe89-472b-8717-1a0640488213" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{9d5b2749-c0c4-4483-901e-60ca1fd7f0c8}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ab92c565-5003-4ac3-93a3-a3ce8796a3c0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DA09990-BE16-49A3-8472-996B154A534D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AAB0DB6-AFD0-4A66-89CA-6E109A256425}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED4FE14C-6916-49A5-90ED-BC40585C5D18}"/>
 </file>